--- a/Hindustan Unilever Limited.xlsx
+++ b/Hindustan Unilever Limited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141D0BD7C7E8/Desktop/Finance Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3397" documentId="8_{55E5A010-C6E7-43B9-8866-A3ADBBEB7938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F95266-79AE-44A9-9651-2379570E529B}"/>
+  <xr:revisionPtr revIDLastSave="3428" documentId="8_{55E5A010-C6E7-43B9-8866-A3ADBBEB7938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ECEC56A-8D73-43F5-9F25-2F6CC2ACA8E2}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sheet" sheetId="6" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="237">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -758,7 +758,10 @@
     <t>Britannia Industries</t>
   </si>
   <si>
-    <t>Net Change (NWC)</t>
+    <t>Net Working Capital</t>
+  </si>
+  <si>
+    <t>ΔNet Working Capital</t>
   </si>
 </sst>
 </file>
@@ -777,7 +780,7 @@
     <numFmt numFmtId="170" formatCode="0.0000"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -966,6 +969,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="19">
     <fill>
@@ -1076,7 +1086,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1492,6 +1502,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1504,7 +1525,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1960,30 +1981,6 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="167" fontId="17" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1996,10 +1993,34 @@
     <xf numFmtId="167" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2017,10 +2038,33 @@
     <xf numFmtId="167" fontId="17" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Accent6" xfId="3" builtinId="49"/>
@@ -2311,16 +2355,16 @@
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="227" t="str">
+      <c r="E1" s="230" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
         <v/>
       </c>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
+      <c r="F1" s="230"/>
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2329,15 +2373,15 @@
       <c r="B2" s="3">
         <v>2.1</v>
       </c>
-      <c r="E2" s="228" t="s">
+      <c r="E2" s="231" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="228"/>
-      <c r="G2" s="228"/>
-      <c r="H2" s="228"/>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -11486,13 +11530,13 @@
         <f t="shared" si="20"/>
         <v>2.0515151514793648E-2</v>
       </c>
-      <c r="R19" s="230" t="s">
+      <c r="R19" s="232" t="s">
         <v>229</v>
       </c>
-      <c r="S19" s="231"/>
-      <c r="T19" s="231"/>
-      <c r="U19" s="231"/>
-      <c r="V19" s="231"/>
+      <c r="S19" s="233"/>
+      <c r="T19" s="233"/>
+      <c r="U19" s="233"/>
+      <c r="V19" s="233"/>
       <c r="W19" s="175"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.45">
@@ -11804,13 +11848,13 @@
       <c r="N25" s="202"/>
       <c r="O25" s="202"/>
       <c r="P25" s="202"/>
-      <c r="R25" s="230" t="s">
+      <c r="R25" s="232" t="s">
         <v>222</v>
       </c>
-      <c r="S25" s="231"/>
-      <c r="T25" s="231"/>
-      <c r="U25" s="231"/>
-      <c r="V25" s="232"/>
+      <c r="S25" s="233"/>
+      <c r="T25" s="233"/>
+      <c r="U25" s="233"/>
+      <c r="V25" s="234"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="L26" s="202"/>
@@ -12475,13 +12519,13 @@
       <c r="O39" s="215"/>
       <c r="P39" s="215"/>
       <c r="Q39" s="136"/>
-      <c r="R39" s="230" t="s">
+      <c r="R39" s="232" t="s">
         <v>224</v>
       </c>
-      <c r="S39" s="231"/>
-      <c r="T39" s="231"/>
-      <c r="U39" s="231"/>
-      <c r="V39" s="232"/>
+      <c r="S39" s="233"/>
+      <c r="T39" s="233"/>
+      <c r="U39" s="233"/>
+      <c r="V39" s="234"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.45">
       <c r="L40" s="202"/>
@@ -16944,13 +16988,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A787426-506C-4957-8B2B-2E9D29417EAA}">
-  <dimension ref="B1:Q24"/>
+  <dimension ref="B1:Q25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="1.73046875" customWidth="1"/>
     <col min="2" max="2" width="34.1328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.46484375" bestFit="1" customWidth="1"/>
     <col min="7" max="15" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16974,25 +17018,25 @@
       <c r="O1" s="229"/>
     </row>
     <row r="2" spans="2:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="236" t="str">
+      <c r="B2" s="228" t="str">
         <f>"WACC Calculation for "&amp;'Data Sheet'!B1</f>
         <v>WACC Calculation for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="233" t="str">
+      <c r="C2" s="228"/>
+      <c r="E2" s="225" t="str">
         <f>"Discount Cash-Flow for "&amp;'Data Sheet'!B1</f>
         <v>Discount Cash-Flow for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="234"/>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="M2" s="234"/>
-      <c r="N2" s="234"/>
-      <c r="O2" s="235"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
+      <c r="M2" s="226"/>
+      <c r="N2" s="226"/>
+      <c r="O2" s="227"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B3" s="83" t="s">
@@ -17002,31 +17046,31 @@
         <v>426802</v>
       </c>
       <c r="E3" s="93"/>
-      <c r="F3" s="82">
+      <c r="F3" s="245">
         <v>1</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="245">
         <v>2</v>
       </c>
-      <c r="H3" s="82">
+      <c r="H3" s="245">
         <v>3</v>
       </c>
-      <c r="I3" s="82">
+      <c r="I3" s="245">
         <v>4</v>
       </c>
-      <c r="J3" s="82">
+      <c r="J3" s="245">
         <v>5</v>
       </c>
-      <c r="K3" s="82">
+      <c r="K3" s="245">
         <v>6</v>
       </c>
-      <c r="L3" s="82">
+      <c r="L3" s="245">
         <v>7</v>
       </c>
-      <c r="M3" s="82">
+      <c r="M3" s="245">
         <v>8</v>
       </c>
-      <c r="N3" s="82">
+      <c r="N3" s="245">
         <v>9</v>
       </c>
       <c r="O3" s="104">
@@ -17043,39 +17087,39 @@
       <c r="E4" s="94" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="246">
         <f>'Historical Financial Statement'!C17</f>
         <v>5651</v>
       </c>
-      <c r="G4" s="57">
+      <c r="G4" s="246">
         <f>'Historical Financial Statement'!D17</f>
         <v>6798</v>
       </c>
-      <c r="H4" s="57">
+      <c r="H4" s="246">
         <f>'Historical Financial Statement'!E17</f>
         <v>8113</v>
       </c>
-      <c r="I4" s="57">
+      <c r="I4" s="246">
         <f>'Historical Financial Statement'!F17</f>
         <v>8662</v>
       </c>
-      <c r="J4" s="57">
+      <c r="J4" s="246">
         <f>'Historical Financial Statement'!G17</f>
         <v>10312</v>
       </c>
-      <c r="K4" s="57">
+      <c r="K4" s="246">
         <f>'Historical Financial Statement'!H17</f>
         <v>11478</v>
       </c>
-      <c r="L4" s="57">
+      <c r="L4" s="246">
         <f>'Historical Financial Statement'!I17</f>
         <v>12602</v>
       </c>
-      <c r="M4" s="57">
+      <c r="M4" s="246">
         <f>'Historical Financial Statement'!J17</f>
         <v>13093</v>
       </c>
-      <c r="N4" s="57">
+      <c r="N4" s="246">
         <f>'Historical Financial Statement'!K17</f>
         <v>13022</v>
       </c>
@@ -17095,39 +17139,39 @@
       <c r="E5" s="94" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="247">
         <f>$C7</f>
         <v>0.16552171796397469</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="247">
         <f t="shared" ref="G5:O5" si="0">$C7</f>
         <v>0.16552171796397469</v>
       </c>
-      <c r="H5" s="58">
+      <c r="H5" s="247">
         <f t="shared" si="0"/>
         <v>0.16552171796397469</v>
       </c>
-      <c r="I5" s="58">
+      <c r="I5" s="247">
         <f t="shared" si="0"/>
         <v>0.16552171796397469</v>
       </c>
-      <c r="J5" s="58">
+      <c r="J5" s="247">
         <f t="shared" si="0"/>
         <v>0.16552171796397469</v>
       </c>
-      <c r="K5" s="58">
+      <c r="K5" s="247">
         <f t="shared" si="0"/>
         <v>0.16552171796397469</v>
       </c>
-      <c r="L5" s="58">
+      <c r="L5" s="247">
         <f t="shared" si="0"/>
         <v>0.16552171796397469</v>
       </c>
-      <c r="M5" s="58">
+      <c r="M5" s="247">
         <f t="shared" si="0"/>
         <v>0.16552171796397469</v>
       </c>
-      <c r="N5" s="58">
+      <c r="N5" s="247">
         <f t="shared" si="0"/>
         <v>0.16552171796397469</v>
       </c>
@@ -17147,39 +17191,39 @@
       <c r="E6" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="246">
         <f>'Historical Financial Statement'!C16</f>
         <v>396</v>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="246">
         <f>'Historical Financial Statement'!D16</f>
         <v>478</v>
       </c>
-      <c r="H6" s="57">
+      <c r="H6" s="246">
         <f>'Historical Financial Statement'!E16</f>
         <v>524</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="246">
         <f>'Historical Financial Statement'!F16</f>
         <v>938</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="246">
         <f>'Historical Financial Statement'!G16</f>
         <v>1012</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="246">
         <f>'Historical Financial Statement'!H16</f>
         <v>1025</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="246">
         <f>'Historical Financial Statement'!I16</f>
         <v>1030</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="246">
         <f>'Historical Financial Statement'!J16</f>
         <v>1097</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="246">
         <f>'Historical Financial Statement'!K16</f>
         <v>1122</v>
       </c>
@@ -17199,45 +17243,45 @@
       <c r="E7" s="94" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="108">
-        <f>'Historical Financial Statement'!C78</f>
-        <v>-1024</v>
-      </c>
-      <c r="G7" s="108">
-        <f>'Historical Financial Statement'!D78</f>
-        <v>-853</v>
-      </c>
-      <c r="H7" s="108">
-        <f>'Historical Financial Statement'!E78</f>
-        <v>-728</v>
-      </c>
-      <c r="I7" s="108">
-        <f>'Historical Financial Statement'!F78</f>
-        <v>-765</v>
-      </c>
-      <c r="J7" s="108">
-        <f>'Historical Financial Statement'!G78</f>
-        <v>-4051</v>
-      </c>
-      <c r="K7" s="108">
-        <f>'Historical Financial Statement'!H78</f>
-        <v>-919</v>
-      </c>
-      <c r="L7" s="108">
-        <f>'Historical Financial Statement'!I78</f>
-        <v>-1041</v>
-      </c>
-      <c r="M7" s="108">
-        <f>'Historical Financial Statement'!J78</f>
-        <v>-1318</v>
-      </c>
-      <c r="N7" s="108">
-        <f>'Historical Financial Statement'!K78</f>
-        <v>-1149</v>
+      <c r="F7" s="248">
+        <f>-'Historical Financial Statement'!C78</f>
+        <v>1024</v>
+      </c>
+      <c r="G7" s="248">
+        <f>-'Historical Financial Statement'!D78</f>
+        <v>853</v>
+      </c>
+      <c r="H7" s="248">
+        <f>-'Historical Financial Statement'!E78</f>
+        <v>728</v>
+      </c>
+      <c r="I7" s="248">
+        <f>-'Historical Financial Statement'!F78</f>
+        <v>765</v>
+      </c>
+      <c r="J7" s="248">
+        <f>-'Historical Financial Statement'!G78</f>
+        <v>4051</v>
+      </c>
+      <c r="K7" s="248">
+        <f>-'Historical Financial Statement'!H78</f>
+        <v>919</v>
+      </c>
+      <c r="L7" s="248">
+        <f>-'Historical Financial Statement'!I78</f>
+        <v>1041</v>
+      </c>
+      <c r="M7" s="248">
+        <f>-'Historical Financial Statement'!J78</f>
+        <v>1318</v>
+      </c>
+      <c r="N7" s="248">
+        <f>-'Historical Financial Statement'!K78</f>
+        <v>1149</v>
       </c>
       <c r="O7" s="109">
-        <f>'Historical Financial Statement'!L78</f>
-        <v>-1274</v>
+        <f>-'Historical Financial Statement'!L78</f>
+        <v>1274</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.45">
@@ -17247,48 +17291,48 @@
       <c r="C8" s="86">
         <v>10</v>
       </c>
-      <c r="E8" s="94" t="s">
+      <c r="E8" s="250" t="s">
         <v>235</v>
       </c>
-      <c r="F8" s="108">
+      <c r="F8" s="251">
         <f>SUM('Historical Financial Statement'!C57,'Historical Financial Statement'!C56)-'Historical Financial Statement'!C36</f>
         <v>-2716</v>
       </c>
-      <c r="G8" s="108">
-        <f>(SUM('Historical Financial Statement'!D57,'Historical Financial Statement'!D56)-'Historical Financial Statement'!D36)-F8</f>
-        <v>-791</v>
-      </c>
-      <c r="H8" s="108">
-        <f>(SUM('Historical Financial Statement'!E57,'Historical Financial Statement'!E56)-'Historical Financial Statement'!E36)-G8</f>
-        <v>-2184</v>
-      </c>
-      <c r="I8" s="108">
-        <f>(SUM('Historical Financial Statement'!F57,'Historical Financial Statement'!F56)-'Historical Financial Statement'!F36)-H8</f>
-        <v>-1533</v>
-      </c>
-      <c r="J8" s="108">
-        <f>(SUM('Historical Financial Statement'!G57,'Historical Financial Statement'!G56)-'Historical Financial Statement'!G36)-I8</f>
-        <v>-2063</v>
-      </c>
-      <c r="K8" s="108">
-        <f>(SUM('Historical Financial Statement'!H57,'Historical Financial Statement'!H56)-'Historical Financial Statement'!H36)-J8</f>
-        <v>-979</v>
-      </c>
-      <c r="L8" s="108">
-        <f>(SUM('Historical Financial Statement'!I57,'Historical Financial Statement'!I56)-'Historical Financial Statement'!I36)-K8</f>
-        <v>-1646</v>
-      </c>
-      <c r="M8" s="108">
-        <f>(SUM('Historical Financial Statement'!J57,'Historical Financial Statement'!J56)-'Historical Financial Statement'!J36)-L8</f>
-        <v>-2000</v>
-      </c>
-      <c r="N8" s="108">
-        <f>(SUM('Historical Financial Statement'!K57,'Historical Financial Statement'!K56)-'Historical Financial Statement'!K36)-M8</f>
-        <v>-1387</v>
-      </c>
-      <c r="O8" s="108">
-        <f>(SUM('Historical Financial Statement'!L57,'Historical Financial Statement'!L56)-'Historical Financial Statement'!L36)-N8</f>
-        <v>-4106</v>
+      <c r="G8" s="251">
+        <f>SUM('Historical Financial Statement'!D57,'Historical Financial Statement'!D56)-'Historical Financial Statement'!D36</f>
+        <v>-3507</v>
+      </c>
+      <c r="H8" s="251">
+        <f>SUM('Historical Financial Statement'!E57,'Historical Financial Statement'!E56)-'Historical Financial Statement'!E36</f>
+        <v>-2975</v>
+      </c>
+      <c r="I8" s="251">
+        <f>SUM('Historical Financial Statement'!F57,'Historical Financial Statement'!F56)-'Historical Financial Statement'!F36</f>
+        <v>-3717</v>
+      </c>
+      <c r="J8" s="251">
+        <f>SUM('Historical Financial Statement'!G57,'Historical Financial Statement'!G56)-'Historical Financial Statement'!G36</f>
+        <v>-3596</v>
+      </c>
+      <c r="K8" s="251">
+        <f>SUM('Historical Financial Statement'!H57,'Historical Financial Statement'!H56)-'Historical Financial Statement'!H36</f>
+        <v>-3042</v>
+      </c>
+      <c r="L8" s="251">
+        <f>SUM('Historical Financial Statement'!I57,'Historical Financial Statement'!I56)-'Historical Financial Statement'!I36</f>
+        <v>-2625</v>
+      </c>
+      <c r="M8" s="251">
+        <f>SUM('Historical Financial Statement'!J57,'Historical Financial Statement'!J56)-'Historical Financial Statement'!J36</f>
+        <v>-3646</v>
+      </c>
+      <c r="N8" s="251">
+        <f>SUM('Historical Financial Statement'!K57,'Historical Financial Statement'!K56)-'Historical Financial Statement'!K36</f>
+        <v>-3387</v>
+      </c>
+      <c r="O8" s="252">
+        <f>SUM('Historical Financial Statement'!L57,'Historical Financial Statement'!L56)-'Historical Financial Statement'!L36</f>
+        <v>-5493</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.45">
@@ -17298,48 +17342,48 @@
       <c r="C9" s="87">
         <v>7.2900000000000006E-2</v>
       </c>
-      <c r="E9" s="95" t="s">
-        <v>164</v>
-      </c>
-      <c r="F9" s="222">
-        <f>F4*(1-F5)+F6-(F7+F8)</f>
-        <v>8851.6367717855792</v>
-      </c>
-      <c r="G9" s="222">
-        <f t="shared" ref="G9:O9" si="1">G4*(1-G5)+G6-(G7+G8)</f>
-        <v>7794.7833612809</v>
-      </c>
-      <c r="H9" s="222">
+      <c r="E9" s="244" t="s">
+        <v>236</v>
+      </c>
+      <c r="F9" s="248">
+        <f>IFERROR(F8-E8,F8)</f>
+        <v>-2716</v>
+      </c>
+      <c r="G9" s="248">
+        <f t="shared" ref="G9:O9" si="1">IFERROR(G8-F8,G8)</f>
+        <v>-791</v>
+      </c>
+      <c r="H9" s="248">
         <f t="shared" si="1"/>
-        <v>10206.122302158274</v>
-      </c>
-      <c r="I9" s="222">
+        <v>532</v>
+      </c>
+      <c r="I9" s="248">
         <f t="shared" si="1"/>
-        <v>10464.250878996052</v>
-      </c>
-      <c r="J9" s="222">
+        <v>-742</v>
+      </c>
+      <c r="J9" s="248">
         <f t="shared" si="1"/>
-        <v>15731.140044355492</v>
-      </c>
-      <c r="K9" s="222">
+        <v>121</v>
+      </c>
+      <c r="K9" s="248">
         <f t="shared" si="1"/>
-        <v>12501.141721209498</v>
-      </c>
-      <c r="L9" s="222">
+        <v>554</v>
+      </c>
+      <c r="L9" s="248">
         <f t="shared" si="1"/>
-        <v>14233.09531021799</v>
-      </c>
-      <c r="M9" s="222">
+        <v>417</v>
+      </c>
+      <c r="M9" s="248">
         <f t="shared" si="1"/>
-        <v>15340.824146697678</v>
-      </c>
-      <c r="N9" s="222">
+        <v>-1021</v>
+      </c>
+      <c r="N9" s="248">
         <f t="shared" si="1"/>
-        <v>14524.576188673122</v>
-      </c>
-      <c r="O9" s="222">
+        <v>259</v>
+      </c>
+      <c r="O9" s="109">
         <f t="shared" si="1"/>
-        <v>17646.202628874344</v>
+        <v>-2106</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.45">
@@ -17350,6 +17394,49 @@
         <f>_xlfn.RRI(C8,'BETA Calculation'!G526,'BETA Calculation'!G5)</f>
         <v>9.9098128389498941E-2</v>
       </c>
+      <c r="E10" s="95" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="222">
+        <f>F4*(1-F5)+F6-(-F7+F9)</f>
+        <v>8851.6367717855792</v>
+      </c>
+      <c r="G10" s="222">
+        <f t="shared" ref="G10:O10" si="2">G4*(1-G5)+G6-(-G7+G9)</f>
+        <v>7794.7833612809</v>
+      </c>
+      <c r="H10" s="222">
+        <f t="shared" si="2"/>
+        <v>7490.1223021582728</v>
+      </c>
+      <c r="I10" s="222">
+        <f t="shared" si="2"/>
+        <v>9673.2508789960521</v>
+      </c>
+      <c r="J10" s="222">
+        <f t="shared" si="2"/>
+        <v>13547.140044355492</v>
+      </c>
+      <c r="K10" s="222">
+        <f t="shared" si="2"/>
+        <v>10968.141721209498</v>
+      </c>
+      <c r="L10" s="222">
+        <f t="shared" si="2"/>
+        <v>12170.09531021799</v>
+      </c>
+      <c r="M10" s="222">
+        <f t="shared" si="2"/>
+        <v>14361.824146697678</v>
+      </c>
+      <c r="N10" s="222">
+        <f t="shared" si="2"/>
+        <v>12878.576188673122</v>
+      </c>
+      <c r="O10" s="249">
+        <f t="shared" si="2"/>
+        <v>15646.202628874344</v>
+      </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B11" s="83" t="s">
@@ -17359,13 +17446,6 @@
         <f>('Historical Financial Statement'!L20/'DCF Model'!C4)*(1-'DCF Model'!C7)</f>
         <v>0.22861555953137899</v>
       </c>
-      <c r="E11" s="79" t="s">
-        <v>173</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="102">
-        <v>0.06</v>
-      </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B12" s="83" t="s">
@@ -17376,12 +17456,11 @@
         <v>8.6471010293465628E-2</v>
       </c>
       <c r="E12" s="79" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="102">
-        <f>C16</f>
-        <v>8.6910930054985541E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -17393,61 +17472,26 @@
         <v>0.51801449674952083</v>
       </c>
       <c r="E13" s="79" t="s">
-        <v>177</v>
-      </c>
-      <c r="G13" s="173">
-        <f>O9*(1+G11)/(G12-G11)</f>
-        <v>695069.80057500862</v>
+        <v>156</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="102">
+        <f>C16</f>
+        <v>8.6910930054985541E-2</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.45">
       <c r="C14" s="90"/>
+      <c r="E14" s="79" t="s">
+        <v>177</v>
+      </c>
+      <c r="G14" s="173">
+        <f>O10*(1+G12)/(G13-G12)</f>
+        <v>760497.42105582997</v>
+      </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.45">
       <c r="C15" s="90"/>
-      <c r="E15" s="79" t="s">
-        <v>174</v>
-      </c>
-      <c r="G15" s="103">
-        <f>1/(1+$G12)^F3</f>
-        <v>0.92003859042011038</v>
-      </c>
-      <c r="H15" s="103">
-        <f t="shared" ref="H15:P15" si="2">1/(1+$G12)^G3</f>
-        <v>0.84647100786222351</v>
-      </c>
-      <c r="I15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.77878599290505024</v>
-      </c>
-      <c r="J15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.71651316715128843</v>
-      </c>
-      <c r="K15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.65921976432332041</v>
-      </c>
-      <c r="L15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.60650762274510495</v>
-      </c>
-      <c r="M15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.55801041830945841</v>
-      </c>
-      <c r="N15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.51339111870117027</v>
-      </c>
-      <c r="O15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.47233964118402821</v>
-      </c>
-      <c r="P15" s="103">
-        <f t="shared" si="2"/>
-        <v>0.43457069767449402</v>
-      </c>
       <c r="Q15" s="103"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.45">
@@ -17459,47 +17503,47 @@
         <v>8.6910930054985541E-2</v>
       </c>
       <c r="E16" s="79" t="s">
-        <v>175</v>
-      </c>
-      <c r="G16" s="171">
-        <f>F9*G15</f>
-        <v>8143.8474184244205</v>
-      </c>
-      <c r="H16" s="171">
-        <f t="shared" ref="H16:P16" si="3">G9*H15</f>
-        <v>6598.0581278911341</v>
-      </c>
-      <c r="I16" s="171">
-        <f t="shared" si="3"/>
-        <v>7948.385090796708</v>
-      </c>
-      <c r="J16" s="171">
-        <f t="shared" si="3"/>
-        <v>7497.7735391751148</v>
-      </c>
-      <c r="K16" s="171">
-        <f t="shared" si="3"/>
-        <v>10370.278432577175</v>
-      </c>
-      <c r="L16" s="171">
-        <f t="shared" si="3"/>
-        <v>7582.0377469304221</v>
-      </c>
-      <c r="M16" s="171">
-        <f t="shared" si="3"/>
-        <v>7942.2154678931311</v>
-      </c>
-      <c r="N16" s="171">
-        <f t="shared" si="3"/>
-        <v>7875.8428704710468</v>
-      </c>
-      <c r="O16" s="171">
-        <f t="shared" si="3"/>
-        <v>6860.5331053079426</v>
-      </c>
-      <c r="P16" s="171">
-        <f t="shared" si="3"/>
-        <v>7668.5225877354142</v>
+        <v>174</v>
+      </c>
+      <c r="G16" s="103">
+        <f>1/(1+$G13)^F3</f>
+        <v>0.92003859042011038</v>
+      </c>
+      <c r="H16" s="103">
+        <f>1/(1+$G13)^G3</f>
+        <v>0.84647100786222351</v>
+      </c>
+      <c r="I16" s="103">
+        <f>1/(1+$G13)^H3</f>
+        <v>0.77878599290505024</v>
+      </c>
+      <c r="J16" s="103">
+        <f>1/(1+$G13)^I3</f>
+        <v>0.71651316715128843</v>
+      </c>
+      <c r="K16" s="103">
+        <f>1/(1+$G13)^J3</f>
+        <v>0.65921976432332041</v>
+      </c>
+      <c r="L16" s="103">
+        <f>1/(1+$G13)^K3</f>
+        <v>0.60650762274510495</v>
+      </c>
+      <c r="M16" s="103">
+        <f>1/(1+$G13)^L3</f>
+        <v>0.55801041830945841</v>
+      </c>
+      <c r="N16" s="103">
+        <f>1/(1+$G13)^M3</f>
+        <v>0.51339111870117027</v>
+      </c>
+      <c r="O16" s="103">
+        <f>1/(1+$G13)^N3</f>
+        <v>0.47233964118402821</v>
+      </c>
+      <c r="P16" s="103">
+        <f>1/(1+$G13)^O3</f>
+        <v>0.43457069767449402</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.45">
@@ -17507,46 +17551,84 @@
         <v>155</v>
       </c>
       <c r="E17" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G17" s="171">
+        <f>F10*G16</f>
+        <v>8143.8474184244205</v>
+      </c>
+      <c r="H17" s="171">
+        <f>G10*H16</f>
+        <v>6598.0581278911341</v>
+      </c>
+      <c r="I17" s="171">
+        <f>H10*I16</f>
+        <v>5833.202334066591</v>
+      </c>
+      <c r="J17" s="171">
+        <f>I10*J16</f>
+        <v>6931.0116239584459</v>
+      </c>
+      <c r="K17" s="171">
+        <f>J10*K16</f>
+        <v>8930.5424672950448</v>
+      </c>
+      <c r="L17" s="171">
+        <f>K10*L16</f>
+        <v>6652.2615612621767</v>
+      </c>
+      <c r="M17" s="171">
+        <f>L10*M16</f>
+        <v>6791.039974920719</v>
+      </c>
+      <c r="N17" s="171">
+        <f>M10*N16</f>
+        <v>7373.2329652626013</v>
+      </c>
+      <c r="O17" s="171">
+        <f>N10*O16</f>
+        <v>6083.062055919032</v>
+      </c>
+      <c r="P17" s="171">
+        <f>O10*P16</f>
+        <v>6799.3811923864259</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="E18" s="79" t="s">
         <v>176</v>
       </c>
-      <c r="G17" s="171">
-        <f>G13*P15</f>
-        <v>302056.96816835291</v>
-      </c>
-      <c r="H17" s="171"/>
-      <c r="I17" s="171"/>
-      <c r="J17" s="171"/>
-      <c r="K17" s="171"/>
-      <c r="L17" s="171"/>
-      <c r="M17" s="171"/>
-      <c r="N17" s="171"/>
-      <c r="O17" s="171"/>
-      <c r="P17" s="171"/>
+      <c r="G18" s="171">
+        <f>G14*P16</f>
+        <v>330489.89484788547</v>
+      </c>
+      <c r="H18" s="171"/>
+      <c r="I18" s="171"/>
+      <c r="J18" s="171"/>
+      <c r="K18" s="171"/>
+      <c r="L18" s="171"/>
+      <c r="M18" s="171"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="171"/>
+      <c r="P18" s="171"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="100" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="101"/>
-      <c r="E19" s="79" t="s">
-        <v>178</v>
-      </c>
-      <c r="G19" s="173">
-        <f>SUM(G16:P16,G17)</f>
-        <v>380544.46255555539</v>
-      </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="100" t="s">
         <v>171</v>
       </c>
       <c r="C20" s="101"/>
-      <c r="E20" s="81" t="s">
-        <v>179</v>
-      </c>
-      <c r="G20" s="108">
-        <f>'Historical Financial Statement'!L41-'Historical Financial Statement'!L58</f>
-        <v>-1505</v>
+      <c r="E20" s="79" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" s="173">
+        <f>SUM(G17:P17,G18)</f>
+        <v>400625.53456927207</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
@@ -17554,31 +17636,40 @@
         <v>172</v>
       </c>
       <c r="C21" s="101"/>
-      <c r="E21" s="79" t="s">
+      <c r="E21" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="G21" s="108">
+        <f>'Historical Financial Statement'!L41-'Historical Financial Statement'!L58</f>
+        <v>-1505</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="E22" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="G21" s="173">
-        <f>G19-G20</f>
-        <v>382049.46255555539</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="E22" s="81" t="s">
+      <c r="G22" s="173">
+        <f>G20-G21</f>
+        <v>402130.53456927207</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="E23" s="81" t="s">
         <v>181</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <f>'Data Sheet'!K93</f>
         <v>234.96</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="E24" s="106" t="s">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="E25" s="106" t="s">
         <v>182</v>
       </c>
-      <c r="F24" s="107"/>
-      <c r="G24" s="223">
-        <f>G21/G22</f>
-        <v>1626.0191630726736</v>
+      <c r="F25" s="107"/>
+      <c r="G25" s="223">
+        <f>G22/G23</f>
+        <v>1711.4850807340486</v>
       </c>
     </row>
   </sheetData>
@@ -17623,17 +17714,17 @@
       <c r="L1" s="229"/>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="237" t="str">
+      <c r="B2" s="235" t="str">
         <f>'Data Sheet'!B1</f>
         <v>HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="F2" s="237" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="F2" s="235" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="237"/>
-      <c r="H2" s="237"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="235"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="79" t="s">
@@ -17655,14 +17746,14 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="245" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B4" s="80">
         <v>46313</v>
       </c>
       <c r="C4" s="154">
         <v>1850.2</v>
       </c>
-      <c r="D4" s="244">
+      <c r="D4" s="58">
         <f t="shared" ref="D4:D68" si="0">IFERROR((C4/C5)-1,0)</f>
         <v>1.6202559455154697E-2</v>
       </c>
@@ -17672,7 +17763,7 @@
       <c r="G4" s="154">
         <v>22888.95</v>
       </c>
-      <c r="H4" s="244">
+      <c r="H4" s="58">
         <f t="shared" ref="H4:H68" si="1">IFERROR((G4/G5)-1,0)</f>
         <v>2.3502739974109454E-2</v>
       </c>
@@ -17699,10 +17790,10 @@
         <f t="shared" si="1"/>
         <v>-6.9758819206544587E-3</v>
       </c>
-      <c r="K5" s="238" t="s">
+      <c r="K5" s="236" t="s">
         <v>148</v>
       </c>
-      <c r="L5" s="238"/>
+      <c r="L5" s="236"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" s="80">
@@ -29729,49 +29820,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="226" t="str">
+      <c r="B2" s="238" t="str">
         <f>"COMP Analysis for "&amp;'Data Sheet'!B1</f>
         <v>COMP Analysis for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="226"/>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="226"/>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
-      <c r="M2" s="226"/>
-      <c r="N2" s="226"/>
-      <c r="O2" s="226"/>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="226"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="238"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="238"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="238"/>
     </row>
     <row r="3" spans="2:18" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="119"/>
-      <c r="C3" s="225" t="s">
+      <c r="C3" s="237" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="225"/>
-      <c r="E3" s="225"/>
-      <c r="F3" s="225"/>
-      <c r="G3" s="225"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="237"/>
       <c r="H3" s="112"/>
-      <c r="I3" s="225" t="s">
+      <c r="I3" s="237" t="s">
         <v>187</v>
       </c>
-      <c r="J3" s="225"/>
-      <c r="K3" s="225"/>
-      <c r="L3" s="225"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="M3" s="112"/>
-      <c r="N3" s="225" t="s">
+      <c r="N3" s="237" t="s">
         <v>191</v>
       </c>
-      <c r="O3" s="225"/>
-      <c r="P3" s="225"/>
-      <c r="Q3" s="225"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="237"/>
+      <c r="Q3" s="237"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B4" s="119" t="s">
@@ -30277,12 +30368,12 @@
       </c>
     </row>
     <row r="18" spans="2:17" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="N18" s="225" t="s">
+      <c r="N18" s="237" t="s">
         <v>191</v>
       </c>
-      <c r="O18" s="225"/>
-      <c r="P18" s="225"/>
-      <c r="Q18" s="225"/>
+      <c r="O18" s="237"/>
+      <c r="P18" s="237"/>
+      <c r="Q18" s="237"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B19" s="128" t="str">

--- a/Hindustan Unilever Limited.xlsx
+++ b/Hindustan Unilever Limited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141d0bd7c7e8/Desktop/Finance Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0195A2C6-5113-4C70-A13E-990E5A9D5AC6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sheet" sheetId="6" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="238">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -1536,7 +1536,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1956,12 +1956,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="10" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="167" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2020,18 +2014,6 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="167" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2048,6 +2030,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2367,16 +2361,16 @@
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="240" t="str">
+      <c r="E1" s="234" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
         <v/>
       </c>
-      <c r="F1" s="240"/>
-      <c r="G1" s="240"/>
-      <c r="H1" s="240"/>
-      <c r="I1" s="240"/>
-      <c r="J1" s="240"/>
-      <c r="K1" s="240"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
+      <c r="I1" s="234"/>
+      <c r="J1" s="234"/>
+      <c r="K1" s="234"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2385,15 +2379,15 @@
       <c r="B2" s="3">
         <v>2.1</v>
       </c>
-      <c r="E2" s="241" t="s">
+      <c r="E2" s="235" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="241"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="241"/>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="235"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -5684,25 +5678,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="239" t="str">
+      <c r="B1" s="233" t="str">
         <f>"Historical Financial Statement for "&amp;'Data Sheet'!B1</f>
         <v>Historical Financial Statement for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
-      <c r="N1" s="239"/>
-      <c r="O1" s="239"/>
-      <c r="P1" s="239"/>
-      <c r="Q1" s="239"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
     </row>
     <row r="2" spans="1:23" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="43" t="str">
@@ -8961,24 +8955,24 @@
         <v>1314</v>
       </c>
       <c r="M71" s="193">
-        <f>IF(M37&gt;L37,ABS(M37-L37),-ABS(M37-L37))</f>
-        <v>111.01985814525121</v>
+        <f>IF(M42&gt;L42,ABS(M42-L42),-ABS(M42-L42))</f>
+        <v>-2430.9099241082622</v>
       </c>
       <c r="N71" s="193">
-        <f t="shared" ref="N71:Q71" si="30">IF(N37&gt;M37,ABS(N37-M37),-ABS(N37-M37))</f>
-        <v>1.582987424716265</v>
+        <f t="shared" ref="N71:Q71" si="30">IF(N42&gt;M42,ABS(N42-M42),-ABS(N42-M42))</f>
+        <v>1424.7260805892838</v>
       </c>
       <c r="O71" s="193">
         <f t="shared" si="30"/>
-        <v>5.32884258187201</v>
+        <v>1443.6673968570067</v>
       </c>
       <c r="P71" s="193">
         <f t="shared" si="30"/>
-        <v>9.8741879883327925</v>
+        <v>1644.3968554026433</v>
       </c>
       <c r="Q71" s="193">
         <f t="shared" si="30"/>
-        <v>-14.323011527938363</v>
+        <v>1633.6913700853038</v>
       </c>
     </row>
     <row r="72" spans="2:21" x14ac:dyDescent="0.45">
@@ -9028,23 +9022,23 @@
       </c>
       <c r="M72" s="193">
         <f>SUM(M67:M71)</f>
-        <v>-42.454388030659388</v>
+        <v>-2584.3841702841728</v>
       </c>
       <c r="N72" s="193">
         <f t="shared" ref="N72:Q72" si="31">SUM(N67:N71)</f>
-        <v>-255.55277482404998</v>
+        <v>1167.5903183405176</v>
       </c>
       <c r="O72" s="193">
         <f t="shared" si="31"/>
-        <v>-283.35165032699967</v>
+        <v>1154.986903948135</v>
       </c>
       <c r="P72" s="193">
         <f t="shared" si="31"/>
-        <v>-234.88838885512359</v>
+        <v>1399.6342785591869</v>
       </c>
       <c r="Q72" s="193">
         <f t="shared" si="31"/>
-        <v>-157.77993018751971</v>
+        <v>1490.2344514257225</v>
       </c>
     </row>
     <row r="73" spans="2:21" x14ac:dyDescent="0.45">
@@ -9226,23 +9220,23 @@
       </c>
       <c r="M75" s="194">
         <f>SUM(M66,M72,M73,M74)</f>
-        <v>11571.99918715539</v>
+        <v>9030.0694049018748</v>
       </c>
       <c r="N75" s="194">
         <f t="shared" ref="N75:Q75" si="33">SUM(N66,N72,N73,N74)</f>
-        <v>12256.268138131967</v>
+        <v>13679.411231296534</v>
       </c>
       <c r="O75" s="194">
         <f t="shared" si="33"/>
-        <v>12877.168121404986</v>
+        <v>14315.506675680121</v>
       </c>
       <c r="P75" s="194">
         <f t="shared" si="33"/>
-        <v>13413.301485925382</v>
+        <v>15047.824153339694</v>
       </c>
       <c r="Q75" s="194">
         <f t="shared" si="33"/>
-        <v>14062.570910937546</v>
+        <v>15710.58529255079</v>
       </c>
     </row>
     <row r="76" spans="2:21" x14ac:dyDescent="0.45">
@@ -9309,24 +9303,24 @@
         <v>-1274</v>
       </c>
       <c r="M78" s="193">
-        <f>-((M49-L49)+(M50-L50)+M16)</f>
-        <v>-3482.8007398050399</v>
+        <f>-Calculation!R21</f>
+        <v>-1956.5852042941485</v>
       </c>
       <c r="N78" s="193">
-        <f t="shared" ref="N78:Q78" si="34">-((N49-M49)+(N50-M50)+N16)</f>
-        <v>-2040.0211265373212</v>
+        <f>-Calculation!S21</f>
+        <v>-2032.7670618670995</v>
       </c>
       <c r="O78" s="193">
-        <f t="shared" si="34"/>
-        <v>-1872.7043484801952</v>
+        <f>-Calculation!T21</f>
+        <v>-2160.2532952600482</v>
       </c>
       <c r="P78" s="193">
-        <f t="shared" si="34"/>
-        <v>-2110.3687532656295</v>
+        <f>-Calculation!U21</f>
+        <v>-2338.2443759980706</v>
       </c>
       <c r="Q78" s="193">
-        <f t="shared" si="34"/>
-        <v>-2172.3852663277439</v>
+        <f>-Calculation!V21</f>
+        <v>-2524.800134259699</v>
       </c>
     </row>
     <row r="79" spans="2:21" x14ac:dyDescent="0.45">
@@ -9375,24 +9369,19 @@
         <v>29</v>
       </c>
       <c r="M79" s="193">
-        <f>AVERAGE(C79:L79)</f>
-        <v>76.8</v>
+        <v>0</v>
       </c>
       <c r="N79" s="193">
-        <f t="shared" ref="N79:Q79" si="35">AVERAGE(D79:M79)</f>
-        <v>67.28</v>
+        <v>0</v>
       </c>
       <c r="O79" s="193">
-        <f t="shared" si="35"/>
-        <v>71.407999999999987</v>
+        <v>0</v>
       </c>
       <c r="P79" s="193">
-        <f t="shared" si="35"/>
-        <v>78.148799999999994</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="193">
-        <f t="shared" si="35"/>
-        <v>80.763679999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="2:21" x14ac:dyDescent="0.45">
@@ -9444,20 +9433,16 @@
         <v>0</v>
       </c>
       <c r="N80" s="193">
-        <f>IF(N51&gt;M51,-ABS(N51-M51),ABS(N51-M51))</f>
-        <v>-69.041498287966533</v>
+        <v>0</v>
       </c>
       <c r="O80" s="193">
-        <f t="shared" ref="O80:Q80" si="36">IF(O51&gt;N51,-ABS(O51-N51),ABS(O51-N51))</f>
-        <v>-237.28066477253742</v>
+        <v>0</v>
       </c>
       <c r="P80" s="193">
-        <f t="shared" si="36"/>
-        <v>-328.21057232371913</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="193">
-        <f t="shared" si="36"/>
-        <v>-659.34376320462798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:17" x14ac:dyDescent="0.45">
@@ -9505,25 +9490,20 @@
         <f>'Manual Data'!L18</f>
         <v>22609</v>
       </c>
-      <c r="M81" s="193">
-        <f>IF(M51&gt;L51,-ABS(M51-L51),ABS(M51-L51))</f>
-        <v>2988.4670327398926</v>
+      <c r="M81" s="193" t="s">
+        <v>155</v>
       </c>
       <c r="N81" s="193">
-        <f t="shared" ref="N81:Q81" si="37">-N80</f>
-        <v>69.041498287966533</v>
+        <v>0</v>
       </c>
       <c r="O81" s="193">
-        <f t="shared" si="37"/>
-        <v>237.28066477253742</v>
+        <v>0</v>
       </c>
       <c r="P81" s="193">
-        <f t="shared" si="37"/>
-        <v>328.21057232371913</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="193">
-        <f t="shared" si="37"/>
-        <v>659.34376320462798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="2:17" x14ac:dyDescent="0.45">
@@ -9708,19 +9688,19 @@
         <v>-415.9</v>
       </c>
       <c r="N84" s="193">
-        <f t="shared" ref="N84:Q84" si="38">AVERAGE(D84:M84)</f>
+        <f t="shared" ref="N84:Q84" si="34">AVERAGE(D84:M84)</f>
         <v>-457.48999999999995</v>
       </c>
       <c r="O84" s="193">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>-503.23899999999992</v>
       </c>
       <c r="P84" s="193">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>-553.5628999999999</v>
       </c>
       <c r="Q84" s="193">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>-608.91918999999984</v>
       </c>
     </row>
@@ -9770,24 +9750,19 @@
         <v>-171</v>
       </c>
       <c r="M85" s="193">
-        <f>AVERAGE(C85:L85)</f>
-        <v>-288</v>
+        <v>0</v>
       </c>
       <c r="N85" s="193">
-        <f t="shared" ref="N85:Q85" si="39">AVERAGE(D85:M85)</f>
-        <v>-308.39999999999998</v>
+        <v>0</v>
       </c>
       <c r="O85" s="193">
-        <f t="shared" si="39"/>
-        <v>-320.94</v>
+        <v>0</v>
       </c>
       <c r="P85" s="193">
-        <f t="shared" si="39"/>
-        <v>-328.23400000000004</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="193">
-        <f t="shared" si="39"/>
-        <v>-331.85739999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="2:17" x14ac:dyDescent="0.45">
@@ -9836,24 +9811,19 @@
         <v>298</v>
       </c>
       <c r="M86" s="193">
-        <f>AVERAGE(C86:L86)</f>
-        <v>39.1</v>
+        <v>0</v>
       </c>
       <c r="N86" s="193">
-        <f t="shared" ref="N86:Q86" si="40">AVERAGE(D86:M86)</f>
-        <v>41.010000000000005</v>
+        <v>0</v>
       </c>
       <c r="O86" s="193">
-        <f t="shared" si="40"/>
-        <v>37.811</v>
+        <v>0</v>
       </c>
       <c r="P86" s="193">
-        <f t="shared" si="40"/>
-        <v>41.592100000000002</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="193">
-        <f t="shared" si="40"/>
-        <v>45.751310000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="2:17" x14ac:dyDescent="0.45">
@@ -9968,24 +9938,19 @@
         <v>963</v>
       </c>
       <c r="M88" s="193">
-        <f>AVERAGE(C88:L88)</f>
-        <v>864.2</v>
+        <v>0</v>
       </c>
       <c r="N88" s="193">
-        <f t="shared" ref="N88:Q88" si="41">AVERAGE(D88:M88)</f>
-        <v>881.62000000000012</v>
+        <v>0</v>
       </c>
       <c r="O88" s="193">
-        <f t="shared" si="41"/>
-        <v>1121.9820000000002</v>
+        <v>0</v>
       </c>
       <c r="P88" s="193">
-        <f t="shared" si="41"/>
-        <v>1237.1802000000002</v>
+        <v>0</v>
       </c>
       <c r="Q88" s="193">
-        <f t="shared" si="41"/>
-        <v>1271.4982200000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="2:17" x14ac:dyDescent="0.45">
@@ -10035,23 +10000,23 @@
       </c>
       <c r="M89" s="194">
         <f>SUM(M78:M88)</f>
-        <v>641.87585268728208</v>
+        <v>-1512.4756445417197</v>
       </c>
       <c r="N89" s="194">
-        <f t="shared" ref="N89:Q89" si="42">SUM(N78:N88)</f>
-        <v>-940.42876451365919</v>
+        <f t="shared" ref="N89:Q89" si="35">SUM(N78:N88)</f>
+        <v>-1614.6846998434378</v>
       </c>
       <c r="O89" s="194">
-        <f t="shared" si="42"/>
-        <v>-550.54284558250174</v>
+        <f t="shared" si="35"/>
+        <v>-1748.3527923623546</v>
       </c>
       <c r="P89" s="194">
-        <f t="shared" si="42"/>
-        <v>-669.45167699127273</v>
+        <f t="shared" si="35"/>
+        <v>-1926.0143997237142</v>
       </c>
       <c r="Q89" s="194">
-        <f t="shared" si="42"/>
-        <v>-676.90283640762732</v>
+        <f t="shared" si="35"/>
+        <v>-2095.4735143395828</v>
       </c>
     </row>
     <row r="90" spans="2:17" x14ac:dyDescent="0.45">
@@ -10184,24 +10149,24 @@
         <v>-117</v>
       </c>
       <c r="M93" s="193">
-        <f>Calculation!L87</f>
-        <v>-108.40055537710805</v>
+        <f>L93</f>
+        <v>-117</v>
       </c>
       <c r="N93" s="193">
-        <f>Calculation!M87</f>
-        <v>-61.79137035301391</v>
+        <f t="shared" ref="N93:Q93" si="36">M93</f>
+        <v>-117</v>
       </c>
       <c r="O93" s="193">
-        <f>Calculation!N87</f>
-        <v>-76.296973714057245</v>
+        <f t="shared" si="36"/>
+        <v>-117</v>
       </c>
       <c r="P93" s="193">
-        <f>Calculation!O87</f>
-        <v>-86.463384018630435</v>
+        <f t="shared" si="36"/>
+        <v>-117</v>
       </c>
       <c r="Q93" s="193">
-        <f>Calculation!P87</f>
-        <v>-96.377117929927394</v>
+        <f t="shared" si="36"/>
+        <v>-117</v>
       </c>
     </row>
     <row r="94" spans="2:17" x14ac:dyDescent="0.45">
@@ -10316,24 +10281,19 @@
         <v>-464</v>
       </c>
       <c r="M95" s="193">
-        <f>AVERAGE(C95:K95)</f>
-        <v>-267.55555555555554</v>
+        <v>0</v>
       </c>
       <c r="N95" s="193">
-        <f t="shared" ref="N95:Q95" si="43">AVERAGE(D95:L95)</f>
-        <v>-319.11111111111109</v>
+        <v>0</v>
       </c>
       <c r="O95" s="193">
-        <f t="shared" si="43"/>
-        <v>-348.83950617283949</v>
+        <v>0</v>
       </c>
       <c r="P95" s="193">
-        <f t="shared" si="43"/>
-        <v>-384.2962962962963</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="193">
-        <f t="shared" si="43"/>
-        <v>-383.94513031550076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -10449,23 +10409,23 @@
       </c>
       <c r="M97" s="194">
         <f>SUM(M92:M96)</f>
-        <v>-11747.571861230557</v>
+        <v>-11488.615750297895</v>
       </c>
       <c r="N97" s="194">
-        <f t="shared" ref="N97:Q97" si="44">SUM(N92:N96)</f>
-        <v>-12906.171049745933</v>
+        <f t="shared" ref="N97:Q97" si="37">SUM(N92:N96)</f>
+        <v>-12642.268568281808</v>
       </c>
       <c r="O97" s="194">
-        <f t="shared" si="44"/>
-        <v>-14034.875386648504</v>
+        <f t="shared" si="37"/>
+        <v>-13726.738906761608</v>
       </c>
       <c r="P97" s="194">
-        <f t="shared" si="44"/>
-        <v>-15084.61972842439</v>
+        <f t="shared" si="37"/>
+        <v>-14730.860048109464</v>
       </c>
       <c r="Q97" s="194">
-        <f t="shared" si="44"/>
-        <v>-16223.836816577443</v>
+        <f t="shared" si="37"/>
+        <v>-15860.514568332015</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.45">
@@ -10499,56 +10459,56 @@
         <v>1671</v>
       </c>
       <c r="E99" s="67">
-        <f t="shared" ref="E99:Q99" si="45">D101</f>
+        <f t="shared" ref="E99:Q99" si="38">D101</f>
         <v>1672</v>
       </c>
       <c r="F99" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>1674</v>
       </c>
       <c r="G99" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>4229</v>
       </c>
       <c r="H99" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>2839</v>
       </c>
       <c r="I99" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>2087</v>
       </c>
       <c r="J99" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>1685</v>
       </c>
       <c r="K99" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>1708</v>
       </c>
       <c r="L99" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>7046</v>
       </c>
       <c r="M99" s="194">
-        <f t="shared" si="45"/>
+        <f t="shared" si="38"/>
         <v>3385</v>
       </c>
       <c r="N99" s="194">
-        <f t="shared" si="45"/>
-        <v>3851.3031786121155</v>
+        <f t="shared" si="38"/>
+        <v>-586.02198993774073</v>
       </c>
       <c r="O99" s="194">
-        <f t="shared" si="45"/>
-        <v>2260.97150248449</v>
+        <f t="shared" si="38"/>
+        <v>-1163.564026766453</v>
       </c>
       <c r="P99" s="194">
-        <f t="shared" si="45"/>
-        <v>552.72139165846966</v>
+        <f t="shared" si="38"/>
+        <v>-2323.1490502102952</v>
       </c>
       <c r="Q99" s="194">
-        <f t="shared" si="45"/>
-        <v>-1788.048527831812</v>
+        <f t="shared" si="38"/>
+        <v>-3932.1993447037803</v>
       </c>
     </row>
     <row r="100" spans="1:17" s="31" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -10599,23 +10559,23 @@
       </c>
       <c r="M100" s="194">
         <f>SUM(M97,M89,M75)</f>
-        <v>466.30317861211552</v>
+        <v>-3971.0219899377407</v>
       </c>
       <c r="N100" s="194">
         <f>SUM(N97,N89,N75)</f>
-        <v>-1590.3316761276255</v>
+        <v>-577.5420368287123</v>
       </c>
       <c r="O100" s="194">
         <f>SUM(O97,O89,O75)</f>
-        <v>-1708.2501108260203</v>
+        <v>-1159.5850234438421</v>
       </c>
       <c r="P100" s="194">
         <f>SUM(P97,P89,P75)</f>
-        <v>-2340.7699194902816</v>
+        <v>-1609.0502944934851</v>
       </c>
       <c r="Q100" s="194">
         <f>SUM(Q97,Q89,Q75)</f>
-        <v>-2838.1687420475246</v>
+        <v>-2245.4027901208065</v>
       </c>
     </row>
     <row r="101" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -10635,52 +10595,52 @@
         <v>1674</v>
       </c>
       <c r="F101" s="67">
-        <f t="shared" ref="F101:L101" si="46">SUM(F99:F100)</f>
+        <f t="shared" ref="F101:L101" si="39">SUM(F99:F100)</f>
         <v>4229</v>
       </c>
       <c r="G101" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="39"/>
         <v>2839</v>
       </c>
       <c r="H101" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="39"/>
         <v>2087</v>
       </c>
       <c r="I101" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="39"/>
         <v>1685</v>
       </c>
       <c r="J101" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="39"/>
         <v>1708</v>
       </c>
       <c r="K101" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="39"/>
         <v>7046</v>
       </c>
       <c r="L101" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="39"/>
         <v>3385</v>
       </c>
       <c r="M101" s="194">
-        <f t="shared" ref="M101" si="47">SUM(M99:M100)</f>
-        <v>3851.3031786121155</v>
+        <f t="shared" ref="M101" si="40">SUM(M99:M100)</f>
+        <v>-586.02198993774073</v>
       </c>
       <c r="N101" s="194">
-        <f t="shared" ref="N101" si="48">SUM(N99:N100)</f>
-        <v>2260.97150248449</v>
+        <f t="shared" ref="N101" si="41">SUM(N99:N100)</f>
+        <v>-1163.564026766453</v>
       </c>
       <c r="O101" s="194">
-        <f t="shared" ref="O101" si="49">SUM(O99:O100)</f>
-        <v>552.72139165846966</v>
+        <f t="shared" ref="O101" si="42">SUM(O99:O100)</f>
+        <v>-2323.1490502102952</v>
       </c>
       <c r="P101" s="194">
-        <f t="shared" ref="P101" si="50">SUM(P99:P100)</f>
-        <v>-1788.048527831812</v>
+        <f t="shared" ref="P101" si="43">SUM(P99:P100)</f>
+        <v>-3932.1993447037803</v>
       </c>
       <c r="Q101" s="194">
-        <f t="shared" ref="Q101" si="51">SUM(Q99:Q100)</f>
-        <v>-4626.2172698793365</v>
+        <f t="shared" ref="Q101" si="44">SUM(Q99:Q100)</f>
+        <v>-6177.6021348245868</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.45">
@@ -10700,7 +10660,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19CF31BD-A30C-46CC-926F-298ACE9C6081}">
-  <dimension ref="A3:W93"/>
+  <dimension ref="A3:W86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.3984375" style="99" bestFit="1" customWidth="1"/>
@@ -11542,13 +11502,13 @@
         <f t="shared" si="20"/>
         <v>2.0515151514793648E-2</v>
       </c>
-      <c r="R19" s="242" t="s">
+      <c r="R19" s="236" t="s">
         <v>229</v>
       </c>
-      <c r="S19" s="243"/>
-      <c r="T19" s="243"/>
-      <c r="U19" s="243"/>
-      <c r="V19" s="243"/>
+      <c r="S19" s="237"/>
+      <c r="T19" s="237"/>
+      <c r="U19" s="237"/>
+      <c r="V19" s="237"/>
       <c r="W19" s="168"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.45">
@@ -11860,13 +11820,13 @@
       <c r="N25" s="195"/>
       <c r="O25" s="195"/>
       <c r="P25" s="195"/>
-      <c r="R25" s="242" t="s">
+      <c r="R25" s="236" t="s">
         <v>222</v>
       </c>
-      <c r="S25" s="243"/>
-      <c r="T25" s="243"/>
-      <c r="U25" s="243"/>
-      <c r="V25" s="244"/>
+      <c r="S25" s="237"/>
+      <c r="T25" s="237"/>
+      <c r="U25" s="237"/>
+      <c r="V25" s="238"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="L26" s="195"/>
@@ -12531,13 +12491,13 @@
       <c r="O39" s="208"/>
       <c r="P39" s="208"/>
       <c r="Q39" s="129"/>
-      <c r="R39" s="242" t="s">
+      <c r="R39" s="236" t="s">
         <v>224</v>
       </c>
-      <c r="S39" s="243"/>
-      <c r="T39" s="243"/>
-      <c r="U39" s="243"/>
-      <c r="V39" s="244"/>
+      <c r="S39" s="237"/>
+      <c r="T39" s="237"/>
+      <c r="U39" s="237"/>
+      <c r="V39" s="238"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.45">
       <c r="L40" s="195"/>
@@ -14404,21 +14364,21 @@
       <c r="O80" s="208"/>
       <c r="P80" s="208"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
       <c r="L81" s="195"/>
       <c r="M81" s="195"/>
       <c r="N81" s="195"/>
       <c r="O81" s="195"/>
       <c r="P81" s="195"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
       <c r="L82" s="195"/>
       <c r="M82" s="195"/>
       <c r="N82" s="195"/>
       <c r="O82" s="195"/>
       <c r="P82" s="195"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A83" s="99" t="str">
         <f>'Historical Financial Statement'!B83</f>
         <v>Dividends received</v>
@@ -14484,7 +14444,7 @@
         <v>247.67477614154711</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A84" s="99" t="s">
         <v>215</v>
       </c>
@@ -14549,7 +14509,7 @@
         <v>3.447392264024865E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A85" s="99" t="s">
         <v>216</v>
       </c>
@@ -14584,298 +14544,12 @@
       <c r="O85" s="208"/>
       <c r="P85" s="208"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
       <c r="L86" s="195"/>
       <c r="M86" s="195"/>
       <c r="N86" s="195"/>
       <c r="O86" s="195"/>
       <c r="P86" s="195"/>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A87" s="99" t="str">
-        <f>'Historical Financial Statement'!B93</f>
-        <v>Interest paid fin</v>
-      </c>
-      <c r="B87" s="99"/>
-      <c r="C87" s="99"/>
-      <c r="D87" s="99"/>
-      <c r="E87" s="99">
-        <f>'Historical Financial Statement'!F93</f>
-        <v>-80</v>
-      </c>
-      <c r="F87" s="99">
-        <f>'Historical Financial Statement'!G93</f>
-        <v>-86</v>
-      </c>
-      <c r="G87" s="99">
-        <f>'Historical Financial Statement'!H93</f>
-        <v>-77</v>
-      </c>
-      <c r="H87" s="99">
-        <f>'Historical Financial Statement'!I93</f>
-        <v>-76</v>
-      </c>
-      <c r="I87" s="99">
-        <f>'Historical Financial Statement'!J93</f>
-        <v>-98</v>
-      </c>
-      <c r="J87" s="99">
-        <f>'Historical Financial Statement'!K93</f>
-        <v>-118</v>
-      </c>
-      <c r="K87" s="99">
-        <f>'Historical Financial Statement'!L93</f>
-        <v>-117</v>
-      </c>
-      <c r="L87" s="201">
-        <f>K88*F90</f>
-        <v>-108.40055537710805</v>
-      </c>
-      <c r="M87" s="211">
-        <f t="shared" ref="M87:Q87" si="99">L88*G90</f>
-        <v>-61.79137035301391</v>
-      </c>
-      <c r="N87" s="211">
-        <f t="shared" si="99"/>
-        <v>-76.296973714057245</v>
-      </c>
-      <c r="O87" s="211">
-        <f t="shared" si="99"/>
-        <v>-86.463384018630435</v>
-      </c>
-      <c r="P87" s="211">
-        <f t="shared" si="99"/>
-        <v>-96.377117929927394</v>
-      </c>
-      <c r="Q87" s="212">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A88" s="99" t="str">
-        <f>'Historical Financial Statement'!B95</f>
-        <v>Financial liabilities</v>
-      </c>
-      <c r="B88" s="99">
-        <f>'Historical Financial Statement'!C95</f>
-        <v>0</v>
-      </c>
-      <c r="C88" s="99">
-        <f>'Historical Financial Statement'!D95</f>
-        <v>0</v>
-      </c>
-      <c r="D88" s="99">
-        <f>'Historical Financial Statement'!E95</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="99">
-        <f>'Historical Financial Statement'!F95</f>
-        <v>-352</v>
-      </c>
-      <c r="F88" s="99">
-        <f>'Historical Financial Statement'!G95</f>
-        <v>-383</v>
-      </c>
-      <c r="G88" s="99">
-        <f>'Historical Financial Statement'!H95</f>
-        <v>-388</v>
-      </c>
-      <c r="H88" s="99">
-        <f>'Historical Financial Statement'!I95</f>
-        <v>-431</v>
-      </c>
-      <c r="I88" s="99">
-        <f>'Historical Financial Statement'!J95</f>
-        <v>-394</v>
-      </c>
-      <c r="J88" s="99">
-        <f>'Historical Financial Statement'!K95</f>
-        <v>-460</v>
-      </c>
-      <c r="K88" s="99">
-        <f>'Historical Financial Statement'!L95</f>
-        <v>-464</v>
-      </c>
-      <c r="L88" s="201">
-        <f>'Historical Financial Statement'!M95</f>
-        <v>-267.55555555555554</v>
-      </c>
-      <c r="M88" s="201">
-        <f>'Historical Financial Statement'!N95</f>
-        <v>-319.11111111111109</v>
-      </c>
-      <c r="N88" s="201">
-        <f>'Historical Financial Statement'!O95</f>
-        <v>-348.83950617283949</v>
-      </c>
-      <c r="O88" s="201">
-        <f>'Historical Financial Statement'!P95</f>
-        <v>-384.2962962962963</v>
-      </c>
-      <c r="P88" s="201">
-        <f>'Historical Financial Statement'!Q95</f>
-        <v>-383.94513031550076</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A89" s="99" t="s">
-        <v>215</v>
-      </c>
-      <c r="E89" s="163"/>
-      <c r="F89" s="163">
-        <f>F87/E88</f>
-        <v>0.24431818181818182</v>
-      </c>
-      <c r="G89" s="163">
-        <f t="shared" ref="G89:J89" si="100">G87/F88</f>
-        <v>0.20104438642297651</v>
-      </c>
-      <c r="H89" s="163">
-        <f t="shared" si="100"/>
-        <v>0.19587628865979381</v>
-      </c>
-      <c r="I89" s="163">
-        <f t="shared" si="100"/>
-        <v>0.22737819025522041</v>
-      </c>
-      <c r="J89" s="163">
-        <f t="shared" si="100"/>
-        <v>0.29949238578680204</v>
-      </c>
-      <c r="K89" s="163"/>
-      <c r="L89" s="200">
-        <f>L87/K88</f>
-        <v>0.23362188658859492</v>
-      </c>
-      <c r="M89" s="207">
-        <f t="shared" ref="M89:O89" si="101">M87/L88</f>
-        <v>0.23094781278119819</v>
-      </c>
-      <c r="N89" s="207">
-        <f t="shared" si="101"/>
-        <v>0.2390921878226028</v>
-      </c>
-      <c r="O89" s="207">
-        <f t="shared" si="101"/>
-        <v>0.24786006885295392</v>
-      </c>
-      <c r="P89" s="207">
-        <f t="shared" ref="P89" si="102">P87/P88</f>
-        <v>0.25101794584744713</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A90" s="99" t="s">
-        <v>216</v>
-      </c>
-      <c r="E90" s="163"/>
-      <c r="F90" s="163">
-        <f>AVERAGE(F89:J89)</f>
-        <v>0.23362188658859492</v>
-      </c>
-      <c r="G90" s="163">
-        <f>AVERAGE(G89:K89)</f>
-        <v>0.23094781278119819</v>
-      </c>
-      <c r="H90" s="163">
-        <f>AVERAGE(H89:L89)</f>
-        <v>0.2390921878226028</v>
-      </c>
-      <c r="I90" s="163">
-        <f>AVERAGE(I89:M89)</f>
-        <v>0.24786006885295392</v>
-      </c>
-      <c r="J90" s="163">
-        <f>AVERAGE(J89:N89)</f>
-        <v>0.2507885682447995</v>
-      </c>
-      <c r="K90" s="163"/>
-      <c r="L90" s="196"/>
-      <c r="M90" s="208"/>
-      <c r="N90" s="208"/>
-      <c r="O90" s="208"/>
-      <c r="P90" s="208"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="L91" s="195"/>
-      <c r="M91" s="195"/>
-      <c r="N91" s="195"/>
-      <c r="O91" s="195"/>
-      <c r="P91" s="195"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="L92" s="195"/>
-      <c r="M92" s="195"/>
-      <c r="N92" s="195"/>
-      <c r="O92" s="195"/>
-      <c r="P92" s="195"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A93" s="99" t="str">
-        <f>'Historical Financial Statement'!B42</f>
-        <v>Other Liabilities</v>
-      </c>
-      <c r="B93" s="99">
-        <f>'Historical Financial Statement'!C42</f>
-        <v>2185</v>
-      </c>
-      <c r="C93" s="99">
-        <f>'Historical Financial Statement'!D42</f>
-        <v>3006</v>
-      </c>
-      <c r="D93" s="99">
-        <f>'Historical Financial Statement'!E42</f>
-        <v>3097</v>
-      </c>
-      <c r="E93" s="99">
-        <f>'Historical Financial Statement'!F42</f>
-        <v>4018</v>
-      </c>
-      <c r="F93" s="99">
-        <f>'Historical Financial Statement'!G42</f>
-        <v>11019</v>
-      </c>
-      <c r="G93" s="99">
-        <f>'Historical Financial Statement'!H42</f>
-        <v>11029</v>
-      </c>
-      <c r="H93" s="99">
-        <f>'Historical Financial Statement'!I42</f>
-        <v>11088</v>
-      </c>
-      <c r="I93" s="99">
-        <f>'Historical Financial Statement'!J42</f>
-        <v>14492</v>
-      </c>
-      <c r="J93" s="99">
-        <f>'Historical Financial Statement'!K42</f>
-        <v>16625</v>
-      </c>
-      <c r="K93" s="99">
-        <f>'Historical Financial Statement'!L42</f>
-        <v>14521</v>
-      </c>
-      <c r="L93" s="198">
-        <f>L54+ABS('Historical Financial Statement'!M45-'Historical Financial Statement'!M61)</f>
-        <v>12090.090075891738</v>
-      </c>
-      <c r="M93" s="198">
-        <f>M54+ABS('Historical Financial Statement'!N45-'Historical Financial Statement'!N61)</f>
-        <v>13514.816156481022</v>
-      </c>
-      <c r="N93" s="198">
-        <f>N54+ABS('Historical Financial Statement'!O45-'Historical Financial Statement'!O61)</f>
-        <v>14958.483553338028</v>
-      </c>
-      <c r="O93" s="198">
-        <f>O54+ABS('Historical Financial Statement'!P45-'Historical Financial Statement'!P61)</f>
-        <v>16602.880408740672</v>
-      </c>
-      <c r="P93" s="198">
-        <f>P54+ABS('Historical Financial Statement'!Q45-'Historical Financial Statement'!Q61)</f>
-        <v>18236.571778825975</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14900,25 +14574,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="239" t="str">
+      <c r="B1" s="233" t="str">
         <f>"Ratio Analysis for "&amp;'Data Sheet'!B1</f>
         <v>Ratio Analysis for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
-      <c r="N1" s="239"/>
-      <c r="O1" s="239"/>
-      <c r="P1" s="239"/>
-      <c r="Q1" s="239"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
     </row>
     <row r="2" spans="2:18" s="44" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="43" t="str">
@@ -17012,36 +16686,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="239" t="str">
+      <c r="B1" s="233" t="str">
         <f>"DCF Model for "&amp;'Data Sheet'!B1</f>
         <v>DCF Model for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
     </row>
     <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="238" t="str">
+      <c r="B2" s="242" t="str">
         <f>"WACC Calculation for "&amp;'Data Sheet'!B1</f>
         <v>WACC Calculation for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="238"/>
-      <c r="E2" s="235" t="str">
+      <c r="C2" s="242"/>
+      <c r="E2" s="239" t="str">
         <f>"Discount Cash-Flow for "&amp;'Data Sheet'!B1</f>
         <v>Discount Cash-Flow for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="237"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B3" s="83" t="s">
@@ -17050,8 +16724,8 @@
       <c r="C3" s="84">
         <v>426802</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="218">
+      <c r="E3" s="215"/>
+      <c r="F3" s="216">
         <v>0</v>
       </c>
       <c r="G3" s="82">
@@ -17066,7 +16740,7 @@
       <c r="J3" s="82">
         <v>4</v>
       </c>
-      <c r="K3" s="219">
+      <c r="K3" s="217">
         <v>5</v>
       </c>
     </row>
@@ -17077,30 +16751,30 @@
       <c r="C4" s="84">
         <v>1325</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="218" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="221">
+      <c r="F4" s="219">
         <f>'Historical Financial Statement'!L17</f>
         <v>13278</v>
       </c>
-      <c r="G4" s="222">
+      <c r="G4" s="220">
         <f>'Historical Financial Statement'!M17</f>
         <v>16015.487501657579</v>
       </c>
-      <c r="H4" s="222">
+      <c r="H4" s="220">
         <f>'Historical Financial Statement'!N17</f>
         <v>17105.502675785319</v>
       </c>
-      <c r="I4" s="222">
+      <c r="I4" s="220">
         <f>'Historical Financial Statement'!O17</f>
         <v>17912.254510547842</v>
       </c>
-      <c r="J4" s="222">
+      <c r="J4" s="220">
         <f>'Historical Financial Statement'!P17</f>
         <v>18472.558984101619</v>
       </c>
-      <c r="K4" s="223">
+      <c r="K4" s="221">
         <f>'Historical Financial Statement'!Q17</f>
         <v>19219.400010032186</v>
       </c>
@@ -17113,30 +16787,30 @@
         <f>C3/SUM(C3:C4)</f>
         <v>0.99690512394686626</v>
       </c>
-      <c r="E5" s="220" t="s">
+      <c r="E5" s="218" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="224">
+      <c r="F5" s="222">
         <f>C7</f>
         <v>0.25169999999999998</v>
       </c>
-      <c r="G5" s="225">
+      <c r="G5" s="223">
         <f>$C7</f>
         <v>0.25169999999999998</v>
       </c>
-      <c r="H5" s="225">
+      <c r="H5" s="223">
         <f t="shared" ref="H5:K5" si="0">$C7</f>
         <v>0.25169999999999998</v>
       </c>
-      <c r="I5" s="225">
+      <c r="I5" s="223">
         <f t="shared" si="0"/>
         <v>0.25169999999999998</v>
       </c>
-      <c r="J5" s="225">
+      <c r="J5" s="223">
         <f t="shared" si="0"/>
         <v>0.25169999999999998</v>
       </c>
-      <c r="K5" s="226">
+      <c r="K5" s="224">
         <f t="shared" si="0"/>
         <v>0.25169999999999998</v>
       </c>
@@ -17149,30 +16823,30 @@
         <f>C4/SUM(C3:C4)</f>
         <v>3.0948760531337664E-3</v>
       </c>
-      <c r="E6" s="220" t="s">
+      <c r="E6" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="221">
+      <c r="F6" s="219">
         <f>'Historical Financial Statement'!L16</f>
         <v>1186</v>
       </c>
-      <c r="G6" s="222">
+      <c r="G6" s="220">
         <f>'Historical Financial Statement'!M16</f>
         <v>1089.70507711338</v>
       </c>
-      <c r="H6" s="222">
+      <c r="H6" s="220">
         <f>'Historical Financial Statement'!N16</f>
         <v>1113.2103481936413</v>
       </c>
-      <c r="I6" s="222">
+      <c r="I6" s="220">
         <f>'Historical Financial Statement'!O16</f>
         <v>1136.5065919769022</v>
       </c>
-      <c r="J6" s="222">
+      <c r="J6" s="220">
         <f>'Historical Financial Statement'!P16</f>
         <v>1162.9513963260688</v>
       </c>
-      <c r="K6" s="223">
+      <c r="K6" s="221">
         <f>'Historical Financial Statement'!Q16</f>
         <v>1184.6399708059155</v>
       </c>
@@ -17185,32 +16859,32 @@
         <f>0.2517</f>
         <v>0.25169999999999998</v>
       </c>
-      <c r="E7" s="220" t="s">
+      <c r="E7" s="218" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="221">
+      <c r="F7" s="219">
         <f>-'Historical Financial Statement'!L78</f>
         <v>1274</v>
       </c>
-      <c r="G7" s="222">
+      <c r="G7" s="220">
         <f>-'Historical Financial Statement'!M78</f>
-        <v>3482.8007398050399</v>
-      </c>
-      <c r="H7" s="222">
+        <v>1956.5852042941485</v>
+      </c>
+      <c r="H7" s="220">
         <f>-'Historical Financial Statement'!N78</f>
-        <v>2040.0211265373212</v>
-      </c>
-      <c r="I7" s="222">
+        <v>2032.7670618670995</v>
+      </c>
+      <c r="I7" s="220">
         <f>-'Historical Financial Statement'!O78</f>
-        <v>1872.7043484801952</v>
-      </c>
-      <c r="J7" s="222">
+        <v>2160.2532952600482</v>
+      </c>
+      <c r="J7" s="220">
         <f>-'Historical Financial Statement'!P78</f>
-        <v>2110.3687532656295</v>
-      </c>
-      <c r="K7" s="223">
+        <v>2338.2443759980706</v>
+      </c>
+      <c r="K7" s="221">
         <f>-'Historical Financial Statement'!Q78</f>
-        <v>2172.3852663277439</v>
+        <v>2524.800134259699</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.45">
@@ -17220,30 +16894,30 @@
       <c r="C8" s="86">
         <v>10</v>
       </c>
-      <c r="E8" s="227" t="s">
+      <c r="E8" s="225" t="s">
         <v>235</v>
       </c>
-      <c r="F8" s="228">
+      <c r="F8" s="226">
         <f>SUM('Historical Financial Statement'!L56:L57)-'Historical Financial Statement'!L36</f>
         <v>-5493</v>
       </c>
-      <c r="G8" s="228">
+      <c r="G8" s="226">
         <f>SUM('Historical Financial Statement'!M56:M57)-'Historical Financial Statement'!M36</f>
         <v>-5234.7542981079141</v>
       </c>
-      <c r="H8" s="228">
+      <c r="H8" s="226">
         <f>SUM('Historical Financial Statement'!N56:N57)-'Historical Financial Statement'!N36</f>
         <v>-5443.2181537300639</v>
       </c>
-      <c r="I8" s="228">
+      <c r="I8" s="226">
         <f>SUM('Historical Financial Statement'!O56:O57)-'Historical Financial Statement'!O36</f>
         <v>-5509.3668032234837</v>
       </c>
-      <c r="J8" s="228">
+      <c r="J8" s="226">
         <f>SUM('Historical Financial Statement'!P56:P57)-'Historical Financial Statement'!P36</f>
         <v>-5723.9673603144802</v>
       </c>
-      <c r="K8" s="229">
+      <c r="K8" s="227">
         <f>SUM('Historical Financial Statement'!Q56:Q57)-'Historical Financial Statement'!Q36</f>
         <v>-5767.6904634181046</v>
       </c>
@@ -17255,7 +16929,7 @@
       <c r="C9" s="87">
         <v>7.2900000000000006E-2</v>
       </c>
-      <c r="E9" s="220" t="s">
+      <c r="E9" s="218" t="s">
         <v>236</v>
       </c>
       <c r="F9" s="63" t="s">
@@ -17277,7 +16951,7 @@
         <f t="shared" si="1"/>
         <v>-214.60055709099652</v>
       </c>
-      <c r="K9" s="230">
+      <c r="K9" s="228">
         <f t="shared" si="1"/>
         <v>-43.723103103624453</v>
       </c>
@@ -17290,29 +16964,29 @@
         <f>_xlfn.RRI(C8,'BETA Calculation'!G526,'BETA Calculation'!G5)</f>
         <v>9.9098128389498941E-2</v>
       </c>
-      <c r="E10" s="231" t="s">
+      <c r="E10" s="229" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="232"/>
-      <c r="G10" s="233">
+      <c r="F10" s="230"/>
+      <c r="G10" s="231">
         <f>G4*(1-G5)+G6-(-G7+G9)</f>
-        <v>16298.649412516701</v>
-      </c>
-      <c r="H10" s="233">
+        <v>14772.433877005809</v>
+      </c>
+      <c r="H10" s="231">
         <f t="shared" ref="H10:K10" si="2">H4*(1-H5)+H6-(-H7+H9)</f>
-        <v>16161.742982643265</v>
-      </c>
-      <c r="I10" s="233">
+        <v>16154.488917973043</v>
+      </c>
+      <c r="I10" s="231">
         <f t="shared" si="2"/>
-        <v>16479.099640193468</v>
-      </c>
-      <c r="J10" s="233">
+        <v>16766.648586973319</v>
+      </c>
+      <c r="J10" s="231">
         <f t="shared" si="2"/>
-        <v>17310.936594485938</v>
-      </c>
-      <c r="K10" s="234">
+        <v>17538.812217218379</v>
+      </c>
+      <c r="K10" s="232">
         <f t="shared" si="2"/>
-        <v>17782.625367744367</v>
+        <v>18135.040235676322</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.45">
@@ -17367,7 +17041,7 @@
       <c r="F14" s="79"/>
       <c r="H14" s="166">
         <f>K10*(1+H12)/(H13-H12)</f>
-        <v>553377.30592717393</v>
+        <v>564344.09998327575</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.45">
@@ -17417,23 +17091,23 @@
       <c r="F17" s="79"/>
       <c r="H17" s="164">
         <f>G10*H16</f>
-        <v>14996.394580286906</v>
+        <v>13592.122986622933</v>
       </c>
       <c r="I17" s="164">
         <f>H10*I16</f>
-        <v>13682.28642286112</v>
+        <v>13676.145241761127</v>
       </c>
       <c r="J17" s="164">
         <f>I10*J16</f>
-        <v>12836.280600487369</v>
+        <v>13060.264862239028</v>
       </c>
       <c r="K17" s="164">
         <f>J10*K16</f>
-        <v>12406.849925536406</v>
+        <v>12570.169722677256</v>
       </c>
       <c r="L17" s="164">
         <f>K10*L16</f>
-        <v>11726.599241404678</v>
+        <v>11958.9961927821</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -17443,7 +17117,7 @@
       <c r="F18" s="79"/>
       <c r="H18" s="164">
         <f>H14*L16</f>
-        <v>364919.90140369738</v>
+        <v>372151.8593513802</v>
       </c>
       <c r="I18" s="164"/>
       <c r="J18" s="164"/>
@@ -17467,7 +17141,7 @@
       <c r="F20" s="79"/>
       <c r="H20" s="166">
         <f>SUM(H17:L17,H18)</f>
-        <v>430568.31217427389</v>
+        <v>437009.55835746264</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -17491,7 +17165,7 @@
       <c r="F22" s="79"/>
       <c r="H22" s="166">
         <f>H20-H21</f>
-        <v>432073.31217427389</v>
+        <v>438514.55835746264</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -17510,9 +17184,9 @@
       </c>
       <c r="F25" s="100"/>
       <c r="G25" s="101"/>
-      <c r="H25" s="215">
+      <c r="H25" s="213">
         <f>H22/H23</f>
-        <v>1838.9228471836648</v>
+        <v>1866.3370716609747</v>
       </c>
     </row>
   </sheetData>
@@ -17541,33 +17215,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="239" t="str">
+      <c r="B1" s="233" t="str">
         <f>"BETA(L) Calculation for "&amp;'Data Sheet'!B1</f>
         <v>BETA(L) Calculation for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="245" t="str">
+      <c r="B2" s="243" t="str">
         <f>'Data Sheet'!B1</f>
         <v>HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="245"/>
-      <c r="D2" s="245"/>
-      <c r="F2" s="245" t="s">
+      <c r="C2" s="243"/>
+      <c r="D2" s="243"/>
+      <c r="F2" s="243" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="245"/>
-      <c r="H2" s="245"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="79" t="s">
@@ -17633,10 +17307,10 @@
         <f t="shared" si="1"/>
         <v>-6.9758819206544587E-3</v>
       </c>
-      <c r="K5" s="246" t="s">
+      <c r="K5" s="244" t="s">
         <v>148</v>
       </c>
-      <c r="L5" s="246"/>
+      <c r="L5" s="244"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" s="80">
@@ -29663,49 +29337,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="248" t="str">
+      <c r="B2" s="246" t="str">
         <f>"COMP Analysis for "&amp;'Data Sheet'!B1</f>
         <v>COMP Analysis for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="248"/>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="M2" s="248"/>
-      <c r="N2" s="248"/>
-      <c r="O2" s="248"/>
-      <c r="P2" s="248"/>
-      <c r="Q2" s="248"/>
+      <c r="C2" s="246"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="246"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="M2" s="246"/>
+      <c r="N2" s="246"/>
+      <c r="O2" s="246"/>
+      <c r="P2" s="246"/>
+      <c r="Q2" s="246"/>
     </row>
     <row r="3" spans="2:18" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="112"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="245" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
-      <c r="G3" s="247"/>
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="245"/>
       <c r="H3" s="105"/>
-      <c r="I3" s="247" t="s">
+      <c r="I3" s="245" t="s">
         <v>187</v>
       </c>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
       <c r="M3" s="105"/>
-      <c r="N3" s="247" t="s">
+      <c r="N3" s="245" t="s">
         <v>191</v>
       </c>
-      <c r="O3" s="247"/>
-      <c r="P3" s="247"/>
-      <c r="Q3" s="247"/>
+      <c r="O3" s="245"/>
+      <c r="P3" s="245"/>
+      <c r="Q3" s="245"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B4" s="112" t="s">
@@ -29821,7 +29495,7 @@
       <c r="E6" s="123">
         <v>327771</v>
       </c>
-      <c r="F6" s="213">
+      <c r="F6" s="211">
         <f>2162-2136</f>
         <v>26</v>
       </c>
@@ -29872,7 +29546,7 @@
       <c r="E7" s="123">
         <v>232943</v>
       </c>
-      <c r="F7" s="213">
+      <c r="F7" s="211">
         <f>444-1341</f>
         <v>-897</v>
       </c>
@@ -29923,7 +29597,7 @@
       <c r="E8" s="123">
         <v>138659</v>
       </c>
-      <c r="F8" s="213">
+      <c r="F8" s="211">
         <f>404-1600</f>
         <v>-1196</v>
       </c>
@@ -29974,7 +29648,7 @@
       <c r="E9" s="123">
         <v>112654</v>
       </c>
-      <c r="F9" s="213">
+      <c r="F9" s="211">
         <f>1348-91</f>
         <v>1257</v>
       </c>
@@ -30211,12 +29885,12 @@
       </c>
     </row>
     <row r="18" spans="2:17" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="N18" s="247" t="s">
+      <c r="N18" s="245" t="s">
         <v>191</v>
       </c>
-      <c r="O18" s="247"/>
-      <c r="P18" s="247"/>
-      <c r="Q18" s="247"/>
+      <c r="O18" s="245"/>
+      <c r="P18" s="245"/>
+      <c r="Q18" s="245"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B19" s="121" t="str">
@@ -30261,19 +29935,19 @@
       <c r="B21" s="81" t="s">
         <v>179</v>
       </c>
-      <c r="N21" s="216">
+      <c r="N21" s="214">
         <f>$F5</f>
         <v>-1505</v>
       </c>
-      <c r="O21" s="216">
+      <c r="O21" s="214">
         <f t="shared" ref="O21:Q21" si="13">$F5</f>
         <v>-1505</v>
       </c>
-      <c r="P21" s="216">
+      <c r="P21" s="214">
         <f t="shared" si="13"/>
         <v>-1505</v>
       </c>
-      <c r="Q21" s="216">
+      <c r="Q21" s="214">
         <f t="shared" si="13"/>
         <v>-1505</v>
       </c>
@@ -30335,19 +30009,19 @@
       <c r="K24" s="108"/>
       <c r="L24" s="108"/>
       <c r="M24" s="108"/>
-      <c r="N24" s="214">
+      <c r="N24" s="212">
         <f>N22/N23</f>
         <v>1970.1888961142458</v>
       </c>
-      <c r="O24" s="214">
+      <c r="O24" s="212">
         <f t="shared" ref="O24:Q24" si="16">O22/O23</f>
         <v>1938.907125545644</v>
       </c>
-      <c r="P24" s="214">
+      <c r="P24" s="212">
         <f t="shared" si="16"/>
         <v>1867.0458453392025</v>
       </c>
-      <c r="Q24" s="214">
+      <c r="Q24" s="212">
         <f t="shared" si="16"/>
         <v>2695.6890532596799</v>
       </c>
@@ -30374,25 +30048,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" s="46" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="239" t="str">
+      <c r="B1" s="233" t="str">
         <f>"Dupont Model for "&amp;'Data Sheet'!B1</f>
         <v>Dupont Model for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
-      <c r="N1" s="239"/>
-      <c r="O1" s="239"/>
-      <c r="P1" s="239"/>
-      <c r="Q1" s="239"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
     </row>
     <row r="2" spans="2:17" s="44" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="43" t="str">
@@ -30851,24 +30525,24 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B12" s="249" t="s">
+      <c r="B12" s="247" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="250"/>
-      <c r="D12" s="250"/>
-      <c r="E12" s="250"/>
-      <c r="F12" s="250"/>
-      <c r="G12" s="250"/>
-      <c r="H12" s="250"/>
-      <c r="I12" s="250"/>
-      <c r="J12" s="250"/>
-      <c r="K12" s="250"/>
-      <c r="L12" s="250"/>
-      <c r="M12" s="250"/>
-      <c r="N12" s="250"/>
-      <c r="O12" s="250"/>
-      <c r="P12" s="250"/>
-      <c r="Q12" s="251"/>
+      <c r="C12" s="248"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="248"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="248"/>
+      <c r="J12" s="248"/>
+      <c r="K12" s="248"/>
+      <c r="L12" s="248"/>
+      <c r="M12" s="248"/>
+      <c r="N12" s="248"/>
+      <c r="O12" s="248"/>
+      <c r="P12" s="248"/>
+      <c r="Q12" s="249"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B13" s="53" t="str">
@@ -31002,24 +30676,24 @@
       </c>
     </row>
     <row r="18" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B18" s="249" t="s">
+      <c r="B18" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="250"/>
-      <c r="D18" s="250"/>
-      <c r="E18" s="250"/>
-      <c r="F18" s="250"/>
-      <c r="G18" s="250"/>
-      <c r="H18" s="250"/>
-      <c r="I18" s="250"/>
-      <c r="J18" s="250"/>
-      <c r="K18" s="250"/>
-      <c r="L18" s="250"/>
-      <c r="M18" s="250"/>
-      <c r="N18" s="250"/>
-      <c r="O18" s="250"/>
-      <c r="P18" s="250"/>
-      <c r="Q18" s="251"/>
+      <c r="C18" s="248"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
+      <c r="M18" s="248"/>
+      <c r="N18" s="248"/>
+      <c r="O18" s="248"/>
+      <c r="P18" s="248"/>
+      <c r="Q18" s="249"/>
     </row>
     <row r="19" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="39" t="str">
@@ -31172,20 +30846,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="252" t="str">
+      <c r="B1" s="250" t="str">
         <f>"Common Size Income Statement for "&amp;'Data Sheet'!B1</f>
         <v>Common Size Income Statement for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="253"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="251"/>
     </row>
     <row r="2" spans="2:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="126" t="str">
@@ -32016,20 +31690,20 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="252" t="str">
+      <c r="B22" s="250" t="str">
         <f>"Common Size Balance Sheet for "&amp;'Data Sheet'!B1</f>
         <v>Common Size Balance Sheet for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C22" s="239"/>
-      <c r="D22" s="239"/>
-      <c r="E22" s="239"/>
-      <c r="F22" s="239"/>
-      <c r="G22" s="239"/>
-      <c r="H22" s="239"/>
-      <c r="I22" s="239"/>
-      <c r="J22" s="239"/>
-      <c r="K22" s="239"/>
-      <c r="L22" s="253"/>
+      <c r="C22" s="233"/>
+      <c r="D22" s="233"/>
+      <c r="E22" s="233"/>
+      <c r="F22" s="233"/>
+      <c r="G22" s="233"/>
+      <c r="H22" s="233"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="233"/>
+      <c r="K22" s="233"/>
+      <c r="L22" s="251"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B23" s="126" t="str">

--- a/Hindustan Unilever Limited.xlsx
+++ b/Hindustan Unilever Limited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141d0bd7c7e8/Desktop/Finance Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0195A2C6-5113-4C70-A13E-990E5A9D5AC6}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE6D03E-8E4C-4EB5-9253-0A94148A321A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="238">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -9490,8 +9490,8 @@
         <f>'Manual Data'!L18</f>
         <v>22609</v>
       </c>
-      <c r="M81" s="193" t="s">
-        <v>155</v>
+      <c r="M81" s="193">
+        <v>0</v>
       </c>
       <c r="N81" s="193">
         <v>0</v>
@@ -9684,24 +9684,19 @@
         <v>-3530</v>
       </c>
       <c r="M84" s="193">
-        <f>AVERAGE(C84:L84)</f>
-        <v>-415.9</v>
+        <v>0</v>
       </c>
       <c r="N84" s="193">
-        <f t="shared" ref="N84:Q84" si="34">AVERAGE(D84:M84)</f>
-        <v>-457.48999999999995</v>
+        <v>0</v>
       </c>
       <c r="O84" s="193">
-        <f t="shared" si="34"/>
-        <v>-503.23899999999992</v>
+        <v>0</v>
       </c>
       <c r="P84" s="193">
-        <f t="shared" si="34"/>
-        <v>-553.5628999999999</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="193">
-        <f t="shared" si="34"/>
-        <v>-608.91918999999984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="2:17" x14ac:dyDescent="0.45">
@@ -10000,23 +9995,23 @@
       </c>
       <c r="M89" s="194">
         <f>SUM(M78:M88)</f>
-        <v>-1512.4756445417197</v>
+        <v>-1096.5756445417196</v>
       </c>
       <c r="N89" s="194">
-        <f t="shared" ref="N89:Q89" si="35">SUM(N78:N88)</f>
-        <v>-1614.6846998434378</v>
+        <f t="shared" ref="N89:Q89" si="34">SUM(N78:N88)</f>
+        <v>-1157.1946998434378</v>
       </c>
       <c r="O89" s="194">
-        <f t="shared" si="35"/>
-        <v>-1748.3527923623546</v>
+        <f t="shared" si="34"/>
+        <v>-1245.1137923623546</v>
       </c>
       <c r="P89" s="194">
-        <f t="shared" si="35"/>
-        <v>-1926.0143997237142</v>
+        <f t="shared" si="34"/>
+        <v>-1372.4514997237143</v>
       </c>
       <c r="Q89" s="194">
-        <f t="shared" si="35"/>
-        <v>-2095.4735143395828</v>
+        <f t="shared" si="34"/>
+        <v>-1486.5543243395828</v>
       </c>
     </row>
     <row r="90" spans="2:17" x14ac:dyDescent="0.45">
@@ -10153,19 +10148,19 @@
         <v>-117</v>
       </c>
       <c r="N93" s="193">
-        <f t="shared" ref="N93:Q93" si="36">M93</f>
+        <f t="shared" ref="N93:Q93" si="35">M93</f>
         <v>-117</v>
       </c>
       <c r="O93" s="193">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>-117</v>
       </c>
       <c r="P93" s="193">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>-117</v>
       </c>
       <c r="Q93" s="193">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>-117</v>
       </c>
     </row>
@@ -10412,19 +10407,19 @@
         <v>-11488.615750297895</v>
       </c>
       <c r="N97" s="194">
-        <f t="shared" ref="N97:Q97" si="37">SUM(N92:N96)</f>
+        <f t="shared" ref="N97:Q97" si="36">SUM(N92:N96)</f>
         <v>-12642.268568281808</v>
       </c>
       <c r="O97" s="194">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-13726.738906761608</v>
       </c>
       <c r="P97" s="194">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-14730.860048109464</v>
       </c>
       <c r="Q97" s="194">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-15860.514568332015</v>
       </c>
     </row>
@@ -10459,56 +10454,56 @@
         <v>1671</v>
       </c>
       <c r="E99" s="67">
-        <f t="shared" ref="E99:Q99" si="38">D101</f>
+        <f t="shared" ref="E99:Q99" si="37">D101</f>
         <v>1672</v>
       </c>
       <c r="F99" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>1674</v>
       </c>
       <c r="G99" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>4229</v>
       </c>
       <c r="H99" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>2839</v>
       </c>
       <c r="I99" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>2087</v>
       </c>
       <c r="J99" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>1685</v>
       </c>
       <c r="K99" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>1708</v>
       </c>
       <c r="L99" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>7046</v>
       </c>
       <c r="M99" s="194">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>3385</v>
       </c>
       <c r="N99" s="194">
-        <f t="shared" si="38"/>
-        <v>-586.02198993774073</v>
+        <f t="shared" si="37"/>
+        <v>-170.12198993773927</v>
       </c>
       <c r="O99" s="194">
-        <f t="shared" si="38"/>
-        <v>-1163.564026766453</v>
+        <f t="shared" si="37"/>
+        <v>-290.17402676645179</v>
       </c>
       <c r="P99" s="194">
-        <f t="shared" si="38"/>
-        <v>-2323.1490502102952</v>
+        <f t="shared" si="37"/>
+        <v>-946.52005021029436</v>
       </c>
       <c r="Q99" s="194">
-        <f t="shared" si="38"/>
-        <v>-3932.1993447037803</v>
+        <f t="shared" si="37"/>
+        <v>-2002.0074447037787</v>
       </c>
     </row>
     <row r="100" spans="1:17" s="31" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -10559,23 +10554,23 @@
       </c>
       <c r="M100" s="194">
         <f>SUM(M97,M89,M75)</f>
-        <v>-3971.0219899377407</v>
+        <v>-3555.1219899377393</v>
       </c>
       <c r="N100" s="194">
         <f>SUM(N97,N89,N75)</f>
-        <v>-577.5420368287123</v>
+        <v>-120.05203682871252</v>
       </c>
       <c r="O100" s="194">
         <f>SUM(O97,O89,O75)</f>
-        <v>-1159.5850234438421</v>
+        <v>-656.34602344384257</v>
       </c>
       <c r="P100" s="194">
         <f>SUM(P97,P89,P75)</f>
-        <v>-1609.0502944934851</v>
+        <v>-1055.4873944934843</v>
       </c>
       <c r="Q100" s="194">
         <f>SUM(Q97,Q89,Q75)</f>
-        <v>-2245.4027901208065</v>
+        <v>-1636.4836001208096</v>
       </c>
     </row>
     <row r="101" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -10595,52 +10590,52 @@
         <v>1674</v>
       </c>
       <c r="F101" s="67">
-        <f t="shared" ref="F101:L101" si="39">SUM(F99:F100)</f>
+        <f t="shared" ref="F101:L101" si="38">SUM(F99:F100)</f>
         <v>4229</v>
       </c>
       <c r="G101" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>2839</v>
       </c>
       <c r="H101" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>2087</v>
       </c>
       <c r="I101" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>1685</v>
       </c>
       <c r="J101" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>1708</v>
       </c>
       <c r="K101" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>7046</v>
       </c>
       <c r="L101" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>3385</v>
       </c>
       <c r="M101" s="194">
-        <f t="shared" ref="M101" si="40">SUM(M99:M100)</f>
-        <v>-586.02198993774073</v>
+        <f t="shared" ref="M101" si="39">SUM(M99:M100)</f>
+        <v>-170.12198993773927</v>
       </c>
       <c r="N101" s="194">
-        <f t="shared" ref="N101" si="41">SUM(N99:N100)</f>
-        <v>-1163.564026766453</v>
+        <f t="shared" ref="N101" si="40">SUM(N99:N100)</f>
+        <v>-290.17402676645179</v>
       </c>
       <c r="O101" s="194">
-        <f t="shared" ref="O101" si="42">SUM(O99:O100)</f>
-        <v>-2323.1490502102952</v>
+        <f t="shared" ref="O101" si="41">SUM(O99:O100)</f>
+        <v>-946.52005021029436</v>
       </c>
       <c r="P101" s="194">
-        <f t="shared" ref="P101" si="43">SUM(P99:P100)</f>
-        <v>-3932.1993447037803</v>
+        <f t="shared" ref="P101" si="42">SUM(P99:P100)</f>
+        <v>-2002.0074447037787</v>
       </c>
       <c r="Q101" s="194">
-        <f t="shared" ref="Q101" si="44">SUM(Q99:Q100)</f>
-        <v>-6177.6021348245868</v>
+        <f t="shared" ref="Q101" si="43">SUM(Q99:Q100)</f>
+        <v>-3638.4910448245882</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.45">

--- a/Hindustan Unilever Limited.xlsx
+++ b/Hindustan Unilever Limited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141d0bd7c7e8/Desktop/Finance Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE6D03E-8E4C-4EB5-9253-0A94148A321A}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B45A0CBB-93A6-44F1-8002-F559C2C723F7}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -783,7 +783,7 @@
     <numFmt numFmtId="170" formatCode="0.0000"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -983,6 +983,15 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1536,7 +1545,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2071,6 +2080,9 @@
     <xf numFmtId="167" fontId="17" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="28" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Accent6" xfId="3" builtinId="49"/>
@@ -8348,24 +8360,24 @@
         <v>2830</v>
       </c>
       <c r="M58" s="193">
-        <f>ABS(M45-SUM(M53,M56,M57))</f>
-        <v>2764.9631564295269</v>
+        <f>M101</f>
+        <v>2764.963156429525</v>
       </c>
       <c r="N58" s="193">
-        <f t="shared" ref="N58:Q58" si="22">ABS(N45-SUM(N53,N56,N57))</f>
-        <v>4819.2490368884173</v>
+        <f t="shared" ref="N58:Q58" si="22">N101</f>
+        <v>4819.24903688841</v>
       </c>
       <c r="O58" s="193">
         <f t="shared" si="22"/>
-        <v>6827.1770245997177</v>
+        <v>6827.1770245997213</v>
       </c>
       <c r="P58" s="193">
         <f t="shared" si="22"/>
-        <v>8677.9558673509891</v>
+        <v>8677.9558673509964</v>
       </c>
       <c r="Q58" s="193">
         <f t="shared" si="22"/>
-        <v>10116.478942950489</v>
+        <v>10116.478942950482</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -8418,19 +8430,19 @@
       </c>
       <c r="N59" s="194">
         <f t="shared" si="23"/>
-        <v>12944.025289247089</v>
+        <v>12944.025289247082</v>
       </c>
       <c r="O59" s="194">
         <f t="shared" si="23"/>
-        <v>15439.895505180895</v>
+        <v>15439.895505180899</v>
       </c>
       <c r="P59" s="194">
         <f t="shared" si="23"/>
-        <v>17748.531644619485</v>
+        <v>17748.531644619492</v>
       </c>
       <c r="Q59" s="194">
         <f t="shared" si="23"/>
-        <v>19753.191510205965</v>
+        <v>19753.191510205957</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8494,11 +8506,11 @@
       </c>
       <c r="O61" s="194">
         <f t="shared" si="24"/>
-        <v>85261.512137597165</v>
+        <v>85261.512137597179</v>
       </c>
       <c r="P61" s="194">
         <f t="shared" si="24"/>
-        <v>89305.139340233494</v>
+        <v>89305.139340233509</v>
       </c>
       <c r="Q61" s="194">
         <f t="shared" si="24"/>
@@ -8517,11 +8529,26 @@
       <c r="J62" s="61"/>
       <c r="K62" s="61"/>
       <c r="L62" s="61"/>
-      <c r="M62" s="205"/>
-      <c r="N62" s="205"/>
-      <c r="O62" s="205"/>
-      <c r="P62" s="205"/>
-      <c r="Q62" s="205"/>
+      <c r="M62" s="252" t="str">
+        <f>IF(M61=M45,"OK","ERROR")</f>
+        <v>OK</v>
+      </c>
+      <c r="N62" s="252" t="str">
+        <f t="shared" ref="N62:Q62" si="25">IF(N61=N45,"OK","ERROR")</f>
+        <v>OK</v>
+      </c>
+      <c r="O62" s="252" t="str">
+        <f t="shared" si="25"/>
+        <v>OK</v>
+      </c>
+      <c r="P62" s="252" t="str">
+        <f t="shared" si="25"/>
+        <v>OK</v>
+      </c>
+      <c r="Q62" s="252" t="str">
+        <f t="shared" si="25"/>
+        <v>OK</v>
+      </c>
     </row>
     <row r="63" spans="1:17" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B63" s="158"/>
@@ -8622,24 +8649,24 @@
         <v>14538</v>
       </c>
       <c r="M66" s="193">
-        <f>M17</f>
-        <v>16015.487501657579</v>
+        <f>M17+M16-M20</f>
+        <v>16876.820294430345</v>
       </c>
       <c r="N66" s="193">
-        <f t="shared" ref="N66:Q66" si="25">N17</f>
-        <v>17105.502675785319</v>
+        <f t="shared" ref="N66:Q66" si="26">N17+N16-N20</f>
+        <v>17977.570314729688</v>
       </c>
       <c r="O66" s="193">
-        <f t="shared" si="25"/>
-        <v>17912.254510547842</v>
+        <f t="shared" si="26"/>
+        <v>18789.715960958092</v>
       </c>
       <c r="P66" s="193">
-        <f t="shared" si="25"/>
-        <v>18472.558984101619</v>
+        <f t="shared" si="26"/>
+        <v>19354.758004005766</v>
       </c>
       <c r="Q66" s="193">
-        <f t="shared" si="25"/>
-        <v>19219.400010032186</v>
+        <f t="shared" si="26"/>
+        <v>20125.033872586519</v>
       </c>
     </row>
     <row r="67" spans="2:21" x14ac:dyDescent="0.45">
@@ -8692,19 +8719,19 @@
         <v>220.95926197999779</v>
       </c>
       <c r="N67" s="193">
-        <f t="shared" ref="N67:Q67" si="26">IF(N56&gt;M56,-ABS(N56-M56),ABS(N56-M56))</f>
+        <f t="shared" ref="N67:Q67" si="27">IF(N56&gt;M56,-ABS(N56-M56),ABS(N56-M56))</f>
         <v>-235.34098218797453</v>
       </c>
       <c r="O67" s="193">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-221.21306074340328</v>
       </c>
       <c r="P67" s="193">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-148.83167493984547</v>
       </c>
       <c r="Q67" s="193">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-289.01593906671724</v>
       </c>
     </row>
@@ -8758,19 +8785,19 @@
         <v>-461.31107383798008</v>
       </c>
       <c r="N68" s="193">
-        <f t="shared" ref="N68:Q68" si="27">IF(N57&gt;M57,-ABS(N57-M57),ABS(N57-M57))</f>
+        <f t="shared" ref="N68:Q68" si="28">IF(N57&gt;M57,-ABS(N57-M57),ABS(N57-M57))</f>
         <v>-229.08345831271527</v>
       </c>
       <c r="O68" s="193">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-266.72916747910131</v>
       </c>
       <c r="P68" s="193">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-309.02562174747254</v>
       </c>
       <c r="Q68" s="193">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-277.12085092026518</v>
       </c>
       <c r="U68" s="28" t="s">
@@ -8827,19 +8854,19 @@
         <v>-17.893890034103606</v>
       </c>
       <c r="N69" s="193">
-        <f t="shared" ref="N69:Q69" si="28">IF(N36&gt;M36,ABS(N36-M36),-ABS(N36-M36))</f>
+        <f t="shared" ref="N69:Q69" si="29">IF(N36&gt;M36,ABS(N36-M36),-ABS(N36-M36))</f>
         <v>672.88829612283917</v>
       </c>
       <c r="O69" s="193">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>554.09087771592567</v>
       </c>
       <c r="P69" s="193">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>672.45785377831453</v>
       </c>
       <c r="Q69" s="193">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>609.85989309060642</v>
       </c>
     </row>
@@ -8893,19 +8920,19 @@
         <v>104.7714557161753</v>
       </c>
       <c r="N70" s="193">
-        <f t="shared" ref="N70:Q70" si="29">IF(N52&gt;M52,-ABS(N52-M52),ABS(N52-M52))</f>
+        <f t="shared" ref="N70:Q70" si="30">IF(N52&gt;M52,-ABS(N52-M52),ABS(N52-M52))</f>
         <v>-465.59961787091561</v>
       </c>
       <c r="O70" s="193">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-354.82914240229275</v>
       </c>
       <c r="P70" s="193">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-459.36313393445289</v>
       </c>
       <c r="Q70" s="193">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-187.18002176320533</v>
       </c>
     </row>
@@ -8955,24 +8982,24 @@
         <v>1314</v>
       </c>
       <c r="M71" s="193">
-        <f>IF(M42&gt;L42,ABS(M42-L42),-ABS(M42-L42))</f>
-        <v>-2430.9099241082622</v>
+        <f>SUM((M42-L42),(M37-L37))</f>
+        <v>-2319.8900659630108</v>
       </c>
       <c r="N71" s="193">
-        <f t="shared" ref="N71:Q71" si="30">IF(N42&gt;M42,ABS(N42-M42),-ABS(N42-M42))</f>
-        <v>1424.7260805892838</v>
+        <f t="shared" ref="N71:Q71" si="31">SUM((N42-M42),(N37-M37))</f>
+        <v>1426.3090680140001</v>
       </c>
       <c r="O71" s="193">
-        <f t="shared" si="30"/>
-        <v>1443.6673968570067</v>
+        <f t="shared" si="31"/>
+        <v>1448.9962394388788</v>
       </c>
       <c r="P71" s="193">
-        <f t="shared" si="30"/>
-        <v>1644.3968554026433</v>
+        <f t="shared" si="31"/>
+        <v>1654.271043390976</v>
       </c>
       <c r="Q71" s="193">
-        <f t="shared" si="30"/>
-        <v>1633.6913700853038</v>
+        <f t="shared" si="31"/>
+        <v>1619.3683585573654</v>
       </c>
     </row>
     <row r="72" spans="2:21" x14ac:dyDescent="0.45">
@@ -9022,23 +9049,23 @@
       </c>
       <c r="M72" s="193">
         <f>SUM(M67:M71)</f>
-        <v>-2584.3841702841728</v>
+        <v>-2473.3643121389214</v>
       </c>
       <c r="N72" s="193">
-        <f t="shared" ref="N72:Q72" si="31">SUM(N67:N71)</f>
-        <v>1167.5903183405176</v>
+        <f t="shared" ref="N72:Q72" si="32">SUM(N67:N71)</f>
+        <v>1169.1733057652339</v>
       </c>
       <c r="O72" s="193">
-        <f t="shared" si="31"/>
-        <v>1154.986903948135</v>
+        <f t="shared" si="32"/>
+        <v>1160.3157465300071</v>
       </c>
       <c r="P72" s="193">
-        <f t="shared" si="31"/>
-        <v>1399.6342785591869</v>
+        <f t="shared" si="32"/>
+        <v>1409.5084665475197</v>
       </c>
       <c r="Q72" s="193">
-        <f t="shared" si="31"/>
-        <v>1490.2344514257225</v>
+        <f t="shared" si="32"/>
+        <v>1475.911439897784</v>
       </c>
     </row>
     <row r="73" spans="2:21" x14ac:dyDescent="0.45">
@@ -9091,19 +9118,19 @@
         <v>-4401.0339264715303</v>
       </c>
       <c r="N73" s="193">
-        <f t="shared" ref="N73:Q73" si="32">-N25</f>
+        <f t="shared" ref="N73:Q73" si="33">-N25</f>
         <v>-4593.6817628293038</v>
       </c>
       <c r="O73" s="193">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-4751.7347388158569</v>
       </c>
       <c r="P73" s="193">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-4824.3691093211119</v>
       </c>
       <c r="Q73" s="193">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-4999.0491689071196</v>
       </c>
     </row>
@@ -9220,23 +9247,23 @@
       </c>
       <c r="M75" s="194">
         <f>SUM(M66,M72,M73,M74)</f>
-        <v>9030.0694049018748</v>
+        <v>10002.422055819894</v>
       </c>
       <c r="N75" s="194">
-        <f t="shared" ref="N75:Q75" si="33">SUM(N66,N72,N73,N74)</f>
-        <v>13679.411231296534</v>
+        <f t="shared" ref="N75:Q75" si="34">SUM(N66,N72,N73,N74)</f>
+        <v>14553.06185766562</v>
       </c>
       <c r="O75" s="194">
-        <f t="shared" si="33"/>
-        <v>14315.506675680121</v>
+        <f t="shared" si="34"/>
+        <v>15198.296968672243</v>
       </c>
       <c r="P75" s="194">
-        <f t="shared" si="33"/>
-        <v>15047.824153339694</v>
+        <f t="shared" si="34"/>
+        <v>15939.897361232172</v>
       </c>
       <c r="Q75" s="194">
-        <f t="shared" si="33"/>
-        <v>15710.58529255079</v>
+        <f t="shared" si="34"/>
+        <v>16601.896143577182</v>
       </c>
     </row>
     <row r="76" spans="2:21" x14ac:dyDescent="0.45">
@@ -9430,19 +9457,24 @@
         <v>-23058</v>
       </c>
       <c r="M80" s="193">
-        <v>0</v>
+        <f>IF(M51&gt;L51,-ABS(M51-L51),ABS(M51-L51))</f>
+        <v>2988.4670327398926</v>
       </c>
       <c r="N80" s="193">
-        <v>0</v>
+        <f t="shared" ref="N80:Q80" si="35">IF(N51&gt;M51,-ABS(N51-M51),ABS(N51-M51))</f>
+        <v>-69.041498287966533</v>
       </c>
       <c r="O80" s="193">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>-237.28066477253742</v>
       </c>
       <c r="P80" s="193">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>-328.21057232371913</v>
       </c>
       <c r="Q80" s="193">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>-659.34376320462798</v>
       </c>
     </row>
     <row r="81" spans="2:17" x14ac:dyDescent="0.45">
@@ -9552,24 +9584,19 @@
         <v>431</v>
       </c>
       <c r="M82" s="193">
-        <f>Calculation!L78</f>
-        <v>625.14808293845215</v>
+        <v>0</v>
       </c>
       <c r="N82" s="193">
-        <f>Calculation!M78</f>
-        <v>642.26773894153973</v>
+        <v>0</v>
       </c>
       <c r="O82" s="193">
-        <f>Calculation!N78</f>
-        <v>686.13291385434127</v>
+        <v>0</v>
       </c>
       <c r="P82" s="193">
-        <f>Calculation!O78</f>
-        <v>723.33375740851625</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="193">
-        <f>Calculation!P78</f>
-        <v>790.57103377856913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="2:17" x14ac:dyDescent="0.45">
@@ -9618,24 +9645,24 @@
         <v>230</v>
       </c>
       <c r="M83" s="193">
-        <f>Calculation!L83</f>
-        <v>234.86147681397699</v>
+        <f>M21</f>
+        <v>1798.4905579726733</v>
       </c>
       <c r="N83" s="193">
-        <f>Calculation!M83</f>
-        <v>233.30462308212196</v>
+        <f t="shared" ref="N83:Q83" si="36">N21</f>
+        <v>2135.555215900366</v>
       </c>
       <c r="O83" s="193">
-        <f>Calculation!N83</f>
-        <v>229.00658904335216</v>
+        <f t="shared" si="36"/>
+        <v>2529.3549390534149</v>
       </c>
       <c r="P83" s="193">
-        <f>Calculation!O83</f>
-        <v>242.45911886584003</v>
+        <f t="shared" si="36"/>
+        <v>2963.3208552179121</v>
       </c>
       <c r="Q83" s="193">
-        <f>Calculation!P83</f>
-        <v>247.67477614154711</v>
+        <f t="shared" si="36"/>
+        <v>3411.8705298866935</v>
       </c>
     </row>
     <row r="84" spans="2:17" x14ac:dyDescent="0.45">
@@ -9933,19 +9960,24 @@
         <v>963</v>
       </c>
       <c r="M88" s="193">
-        <v>0</v>
+        <f>IF(M50&gt;L50,-ABS(M50-L50),ABS(M50-L50))</f>
+        <v>-1526.2155355108921</v>
       </c>
       <c r="N88" s="193">
-        <v>0</v>
+        <f t="shared" ref="N88:Q88" si="37">IF(N50&gt;M50,-ABS(N50-M50),ABS(N50-M50))</f>
+        <v>-7.2540646702263984</v>
       </c>
       <c r="O88" s="193">
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>287.54894677984794</v>
       </c>
       <c r="P88" s="193">
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>227.87562273244475</v>
       </c>
       <c r="Q88" s="193">
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>352.4148679319519</v>
       </c>
     </row>
     <row r="89" spans="2:17" x14ac:dyDescent="0.45">
@@ -9995,23 +10027,23 @@
       </c>
       <c r="M89" s="194">
         <f>SUM(M78:M88)</f>
-        <v>-1096.5756445417196</v>
+        <v>1304.1568509075255</v>
       </c>
       <c r="N89" s="194">
-        <f t="shared" ref="N89:Q89" si="34">SUM(N78:N88)</f>
-        <v>-1157.1946998434378</v>
+        <f t="shared" ref="N89:Q89" si="38">SUM(N78:N88)</f>
+        <v>26.492591075073506</v>
       </c>
       <c r="O89" s="194">
-        <f t="shared" si="34"/>
-        <v>-1245.1137923623546</v>
+        <f t="shared" si="38"/>
+        <v>419.36992580067727</v>
       </c>
       <c r="P89" s="194">
-        <f t="shared" si="34"/>
-        <v>-1372.4514997237143</v>
+        <f t="shared" si="38"/>
+        <v>524.74152962856715</v>
       </c>
       <c r="Q89" s="194">
-        <f t="shared" si="34"/>
-        <v>-1486.5543243395828</v>
+        <f t="shared" si="38"/>
+        <v>580.1415003543184</v>
       </c>
     </row>
     <row r="90" spans="2:17" x14ac:dyDescent="0.45">
@@ -10144,24 +10176,23 @@
         <v>-117</v>
       </c>
       <c r="M93" s="193">
-        <f>L93</f>
-        <v>-117</v>
+        <v>0</v>
       </c>
       <c r="N93" s="193">
-        <f t="shared" ref="N93:Q93" si="35">M93</f>
-        <v>-117</v>
+        <f t="shared" ref="N93:Q93" si="39">M93</f>
+        <v>0</v>
       </c>
       <c r="O93" s="193">
-        <f t="shared" si="35"/>
-        <v>-117</v>
+        <f t="shared" si="39"/>
+        <v>0</v>
       </c>
       <c r="P93" s="193">
-        <f t="shared" si="35"/>
-        <v>-117</v>
+        <f t="shared" si="39"/>
+        <v>0</v>
       </c>
       <c r="Q93" s="193">
-        <f t="shared" si="35"/>
-        <v>-117</v>
+        <f t="shared" si="39"/>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="2:17" x14ac:dyDescent="0.45">
@@ -10210,23 +10241,23 @@
         <v>-10103</v>
       </c>
       <c r="M94" s="193">
-        <f>Calculation!L42</f>
+        <f>Calculation!R43</f>
         <v>-11371.615750297895</v>
       </c>
       <c r="N94" s="193">
-        <f>Calculation!M42</f>
+        <f>Calculation!S43</f>
         <v>-12525.268568281808</v>
       </c>
       <c r="O94" s="193">
-        <f>Calculation!N42</f>
+        <f>Calculation!T43</f>
         <v>-13609.738906761608</v>
       </c>
       <c r="P94" s="193">
-        <f>Calculation!O42</f>
+        <f>Calculation!U43</f>
         <v>-14613.860048109464</v>
       </c>
       <c r="Q94" s="193">
-        <f>Calculation!P42</f>
+        <f>Calculation!V43</f>
         <v>-15743.514568332015</v>
       </c>
     </row>
@@ -10404,23 +10435,23 @@
       </c>
       <c r="M97" s="194">
         <f>SUM(M92:M96)</f>
-        <v>-11488.615750297895</v>
+        <v>-11371.615750297895</v>
       </c>
       <c r="N97" s="194">
-        <f t="shared" ref="N97:Q97" si="36">SUM(N92:N96)</f>
-        <v>-12642.268568281808</v>
+        <f t="shared" ref="N97:Q97" si="40">SUM(N92:N96)</f>
+        <v>-12525.268568281808</v>
       </c>
       <c r="O97" s="194">
-        <f t="shared" si="36"/>
-        <v>-13726.738906761608</v>
+        <f t="shared" si="40"/>
+        <v>-13609.738906761608</v>
       </c>
       <c r="P97" s="194">
-        <f t="shared" si="36"/>
-        <v>-14730.860048109464</v>
+        <f t="shared" si="40"/>
+        <v>-14613.860048109464</v>
       </c>
       <c r="Q97" s="194">
-        <f t="shared" si="36"/>
-        <v>-15860.514568332015</v>
+        <f t="shared" si="40"/>
+        <v>-15743.514568332015</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.45">
@@ -10454,56 +10485,56 @@
         <v>1671</v>
       </c>
       <c r="E99" s="67">
-        <f t="shared" ref="E99:Q99" si="37">D101</f>
+        <f t="shared" ref="E99:Q99" si="41">D101</f>
         <v>1672</v>
       </c>
       <c r="F99" s="67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1674</v>
       </c>
       <c r="G99" s="67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>4229</v>
       </c>
       <c r="H99" s="67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>2839</v>
       </c>
       <c r="I99" s="67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>2087</v>
       </c>
       <c r="J99" s="67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1685</v>
       </c>
       <c r="K99" s="67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1708</v>
       </c>
       <c r="L99" s="67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>7046</v>
       </c>
       <c r="M99" s="194">
-        <f t="shared" si="37"/>
-        <v>3385</v>
+        <f>L58</f>
+        <v>2830</v>
       </c>
       <c r="N99" s="194">
-        <f t="shared" si="37"/>
-        <v>-170.12198993773927</v>
+        <f t="shared" si="41"/>
+        <v>2764.963156429525</v>
       </c>
       <c r="O99" s="194">
-        <f t="shared" si="37"/>
-        <v>-290.17402676645179</v>
+        <f t="shared" si="41"/>
+        <v>4819.24903688841</v>
       </c>
       <c r="P99" s="194">
-        <f t="shared" si="37"/>
-        <v>-946.52005021029436</v>
+        <f t="shared" si="41"/>
+        <v>6827.1770245997213</v>
       </c>
       <c r="Q99" s="194">
-        <f t="shared" si="37"/>
-        <v>-2002.0074447037787</v>
+        <f t="shared" si="41"/>
+        <v>8677.9558673509964</v>
       </c>
     </row>
     <row r="100" spans="1:17" s="31" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -10554,23 +10585,23 @@
       </c>
       <c r="M100" s="194">
         <f>SUM(M97,M89,M75)</f>
-        <v>-3555.1219899377393</v>
+        <v>-65.036843570474957</v>
       </c>
       <c r="N100" s="194">
         <f>SUM(N97,N89,N75)</f>
-        <v>-120.05203682871252</v>
+        <v>2054.285880458885</v>
       </c>
       <c r="O100" s="194">
         <f>SUM(O97,O89,O75)</f>
-        <v>-656.34602344384257</v>
+        <v>2007.9279877113113</v>
       </c>
       <c r="P100" s="194">
         <f>SUM(P97,P89,P75)</f>
-        <v>-1055.4873944934843</v>
+        <v>1850.7788427512751</v>
       </c>
       <c r="Q100" s="194">
         <f>SUM(Q97,Q89,Q75)</f>
-        <v>-1636.4836001208096</v>
+        <v>1438.5230755994853</v>
       </c>
     </row>
     <row r="101" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -10590,52 +10621,52 @@
         <v>1674</v>
       </c>
       <c r="F101" s="67">
-        <f t="shared" ref="F101:L101" si="38">SUM(F99:F100)</f>
+        <f t="shared" ref="F101:L101" si="42">SUM(F99:F100)</f>
         <v>4229</v>
       </c>
       <c r="G101" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>2839</v>
       </c>
       <c r="H101" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>2087</v>
       </c>
       <c r="I101" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>1685</v>
       </c>
       <c r="J101" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>1708</v>
       </c>
       <c r="K101" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7046</v>
       </c>
       <c r="L101" s="67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>3385</v>
       </c>
       <c r="M101" s="194">
-        <f t="shared" ref="M101" si="39">SUM(M99:M100)</f>
-        <v>-170.12198993773927</v>
+        <f t="shared" ref="M101" si="43">SUM(M99:M100)</f>
+        <v>2764.963156429525</v>
       </c>
       <c r="N101" s="194">
-        <f t="shared" ref="N101" si="40">SUM(N99:N100)</f>
-        <v>-290.17402676645179</v>
+        <f t="shared" ref="N101" si="44">SUM(N99:N100)</f>
+        <v>4819.24903688841</v>
       </c>
       <c r="O101" s="194">
-        <f t="shared" ref="O101" si="41">SUM(O99:O100)</f>
-        <v>-946.52005021029436</v>
+        <f t="shared" ref="O101" si="45">SUM(O99:O100)</f>
+        <v>6827.1770245997213</v>
       </c>
       <c r="P101" s="194">
-        <f t="shared" ref="P101" si="42">SUM(P99:P100)</f>
-        <v>-2002.0074447037787</v>
+        <f t="shared" ref="P101" si="46">SUM(P99:P100)</f>
+        <v>8677.9558673509964</v>
       </c>
       <c r="Q101" s="194">
-        <f t="shared" ref="Q101" si="43">SUM(Q99:Q100)</f>
-        <v>-3638.4910448245882</v>
+        <f t="shared" ref="Q101" si="47">SUM(Q99:Q100)</f>
+        <v>10116.478942950482</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.45">
@@ -10648,7 +10679,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="M6:Q6 M87:Q87" formula="1"/>
+    <ignoredError sqref="M6:Q6 M87:Q87 M99" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14979,11 +15010,11 @@
       </c>
       <c r="O8" s="72">
         <f>'Historical Financial Statement'!O26/'Historical Financial Statement'!O61</f>
-        <v>0.18098235865575649</v>
+        <v>0.18098235865575646</v>
       </c>
       <c r="P8" s="72">
         <f>'Historical Financial Statement'!P26/'Historical Financial Statement'!P61</f>
-        <v>0.18286470940221927</v>
+        <v>0.18286470940221924</v>
       </c>
       <c r="Q8" s="72">
         <f>'Historical Financial Statement'!Q26/'Historical Financial Statement'!Q61</f>
@@ -15212,11 +15243,11 @@
       </c>
       <c r="O13" s="76">
         <f>'Historical Financial Statement'!O41/'Historical Financial Statement'!O61</f>
-        <v>1.5540423419440202E-2</v>
+        <v>1.5540423419440199E-2</v>
       </c>
       <c r="P13" s="76">
         <f>'Historical Financial Statement'!P41/'Historical Financial Statement'!P61</f>
-        <v>1.4836772102801756E-2</v>
+        <v>1.4836772102801755E-2</v>
       </c>
       <c r="Q13" s="76">
         <f>'Historical Financial Statement'!Q41/'Historical Financial Statement'!Q61</f>
@@ -15379,11 +15410,11 @@
       </c>
       <c r="O17" s="76">
         <f>'Historical Financial Statement'!O5/'Historical Financial Statement'!O61</f>
-        <v>0.90565076960786717</v>
+        <v>0.90565076960786695</v>
       </c>
       <c r="P17" s="76">
         <f>'Historical Financial Statement'!P5/'Historical Financial Statement'!P61</f>
-        <v>0.90693367831818494</v>
+        <v>0.90693367831818472</v>
       </c>
       <c r="Q17" s="76">
         <f>'Historical Financial Statement'!Q5/'Historical Financial Statement'!Q61</f>
@@ -15737,19 +15768,19 @@
       </c>
       <c r="N24" s="72">
         <f>'Historical Financial Statement'!N59/'Historical Financial Statement'!N38</f>
-        <v>0.94615937090595159</v>
+        <v>0.94615937090595115</v>
       </c>
       <c r="O24" s="72">
         <f>'Historical Financial Statement'!O59/'Historical Financial Statement'!O38</f>
-        <v>1.0842610325245658</v>
+        <v>1.0842610325245661</v>
       </c>
       <c r="P24" s="72">
         <f>'Historical Financial Statement'!P59/'Historical Financial Statement'!P38</f>
-        <v>1.1893926102584302</v>
+        <v>1.1893926102584307</v>
       </c>
       <c r="Q24" s="72">
         <f>'Historical Financial Statement'!Q59/'Historical Financial Statement'!Q38</f>
-        <v>1.2729305811049167</v>
+        <v>1.2729305811049163</v>
       </c>
       <c r="R24" s="57"/>
     </row>
@@ -15803,19 +15834,19 @@
       </c>
       <c r="N25" s="72">
         <f>('Historical Financial Statement'!N59-'Historical Financial Statement'!N57)/'Historical Financial Statement'!N38</f>
-        <v>0.57531338817405209</v>
+        <v>0.57531338817405153</v>
       </c>
       <c r="O25" s="72">
         <f>('Historical Financial Statement'!O59-'Historical Financial Statement'!O57)/'Historical Financial Statement'!O38</f>
-        <v>0.70925279270671027</v>
+        <v>0.70925279270671049</v>
       </c>
       <c r="P25" s="72">
         <f>('Historical Financial Statement'!P59-'Historical Financial Statement'!P57)/'Historical Financial Statement'!P38</f>
-        <v>0.8108229014155327</v>
+        <v>0.81082290141553315</v>
       </c>
       <c r="Q25" s="72">
         <f>('Historical Financial Statement'!Q59-'Historical Financial Statement'!Q57)/'Historical Financial Statement'!Q38</f>
-        <v>0.89103125459305743</v>
+        <v>0.89103125459305699</v>
       </c>
       <c r="R25" s="151"/>
     </row>
@@ -15865,23 +15896,23 @@
       </c>
       <c r="M26" s="72">
         <f>'Historical Financial Statement'!M58/'Historical Financial Statement'!M38</f>
-        <v>0.21258929547574393</v>
+        <v>0.21258929547574379</v>
       </c>
       <c r="N26" s="72">
         <f>'Historical Financial Statement'!N58/'Historical Financial Statement'!N38</f>
-        <v>0.35226890670318561</v>
+        <v>0.35226890670318511</v>
       </c>
       <c r="O26" s="72">
         <f>'Historical Financial Statement'!O58/'Historical Financial Statement'!O38</f>
-        <v>0.47943601738992175</v>
+        <v>0.47943601738992203</v>
       </c>
       <c r="P26" s="72">
         <f>'Historical Financial Statement'!P58/'Historical Financial Statement'!P38</f>
-        <v>0.58154087264481069</v>
+        <v>0.58154087264481114</v>
       </c>
       <c r="Q26" s="72">
         <f>'Historical Financial Statement'!Q58/'Historical Financial Statement'!Q38</f>
-        <v>0.65192378724886602</v>
+        <v>0.65192378724886557</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
@@ -30443,11 +30474,11 @@
       </c>
       <c r="O7" s="52">
         <f>'Historical Financial Statement'!O5/'Historical Financial Statement'!O61</f>
-        <v>0.90565076960786717</v>
+        <v>0.90565076960786695</v>
       </c>
       <c r="P7" s="52">
         <f>'Historical Financial Statement'!P5/'Historical Financial Statement'!P61</f>
-        <v>0.90693367831818494</v>
+        <v>0.90693367831818472</v>
       </c>
       <c r="Q7" s="52">
         <f>'Historical Financial Statement'!Q5/'Historical Financial Statement'!Q61</f>
@@ -30508,11 +30539,11 @@
       </c>
       <c r="O8" s="52">
         <f>'Historical Financial Statement'!O61/SUM('Historical Financial Statement'!O31:O32)</f>
-        <v>1.5576289606843192</v>
+        <v>1.5576289606843194</v>
       </c>
       <c r="P8" s="52">
         <f>'Historical Financial Statement'!P61/SUM('Historical Financial Statement'!P31:P32)</f>
-        <v>1.5818843652449779</v>
+        <v>1.5818843652449781</v>
       </c>
       <c r="Q8" s="52">
         <f>'Historical Financial Statement'!Q61/SUM('Historical Financial Statement'!Q31:Q32)</f>
@@ -30659,11 +30690,11 @@
       </c>
       <c r="O14" s="38">
         <f t="shared" si="1"/>
-        <v>0.28190336321516274</v>
+        <v>0.28190336321516268</v>
       </c>
       <c r="P14" s="38">
         <f t="shared" si="1"/>
-        <v>0.28927082475843696</v>
+        <v>0.28927082475843691</v>
       </c>
       <c r="Q14" s="38">
         <f t="shared" si="1"/>
@@ -30810,11 +30841,11 @@
       </c>
       <c r="O20" s="42">
         <f t="shared" si="3"/>
-        <v>0.28190336321516274</v>
+        <v>0.28190336321516268</v>
       </c>
       <c r="P20" s="42">
         <f t="shared" si="3"/>
-        <v>0.28927082475843696</v>
+        <v>0.28927082475843691</v>
       </c>
       <c r="Q20" s="42">
         <f t="shared" si="3"/>

--- a/Hindustan Unilever Limited.xlsx
+++ b/Hindustan Unilever Limited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141d0bd7c7e8/Desktop/Finance Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B45A0CBB-93A6-44F1-8002-F559C2C723F7}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{BDDFAB4B-B0E7-40E0-B05F-878A9435B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04DF4C09-A7F1-4758-AF76-CCCD595885C1}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="894" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sheet" sheetId="6" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="237">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -737,9 +737,6 @@
     <t>Total Non-Current Liabilities</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>Fixed Assets Schedule</t>
   </si>
   <si>
@@ -783,7 +780,7 @@
     <numFmt numFmtId="170" formatCode="0.0000"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -992,6 +989,14 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1545,7 +1550,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2023,6 +2028,22 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="28" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2039,18 +2060,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2079,9 +2088,6 @@
     </xf>
     <xf numFmtId="167" fontId="17" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="28" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2373,16 +2379,16 @@
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="234" t="str">
+      <c r="E1" s="240" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
         <v/>
       </c>
-      <c r="F1" s="234"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
+      <c r="F1" s="240"/>
+      <c r="G1" s="240"/>
+      <c r="H1" s="240"/>
+      <c r="I1" s="240"/>
+      <c r="J1" s="240"/>
+      <c r="K1" s="240"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2391,15 +2397,15 @@
       <c r="B2" s="3">
         <v>2.1</v>
       </c>
-      <c r="E2" s="235" t="s">
+      <c r="E2" s="241" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="235"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="235"/>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -5690,25 +5696,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="233" t="str">
+      <c r="B1" s="239" t="str">
         <f>"Historical Financial Statement for "&amp;'Data Sheet'!B1</f>
         <v>Historical Financial Statement for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
+      <c r="M1" s="239"/>
+      <c r="N1" s="239"/>
+      <c r="O1" s="239"/>
+      <c r="P1" s="239"/>
+      <c r="Q1" s="239"/>
     </row>
     <row r="2" spans="1:23" s="45" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="43" t="str">
@@ -8529,23 +8535,23 @@
       <c r="J62" s="61"/>
       <c r="K62" s="61"/>
       <c r="L62" s="61"/>
-      <c r="M62" s="252" t="str">
+      <c r="M62" s="233" t="str">
         <f>IF(M61=M45,"OK","ERROR")</f>
         <v>OK</v>
       </c>
-      <c r="N62" s="252" t="str">
+      <c r="N62" s="233" t="str">
         <f t="shared" ref="N62:Q62" si="25">IF(N61=N45,"OK","ERROR")</f>
         <v>OK</v>
       </c>
-      <c r="O62" s="252" t="str">
+      <c r="O62" s="233" t="str">
         <f t="shared" si="25"/>
         <v>OK</v>
       </c>
-      <c r="P62" s="252" t="str">
+      <c r="P62" s="233" t="str">
         <f t="shared" si="25"/>
         <v>OK</v>
       </c>
-      <c r="Q62" s="252" t="str">
+      <c r="Q62" s="233" t="str">
         <f t="shared" si="25"/>
         <v>OK</v>
       </c>
@@ -8592,7 +8598,7 @@
       <c r="P64" s="206"/>
       <c r="Q64" s="206"/>
     </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B65" s="24" t="str">
         <f>'Manual Data'!B2</f>
         <v>Cash from Operating Activity </v>
@@ -8603,7 +8609,7 @@
       <c r="P65" s="193"/>
       <c r="Q65" s="193"/>
     </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B66" s="34" t="str">
         <f>'Manual Data'!B3</f>
         <v>Profit from operations</v>
@@ -8669,7 +8675,7 @@
         <v>20125.033872586519</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B67" s="34" t="str">
         <f>'Manual Data'!B4</f>
         <v>Receivables</v>
@@ -8735,7 +8741,7 @@
         <v>-289.01593906671724</v>
       </c>
     </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B68" s="34" t="str">
         <f>'Manual Data'!B5</f>
         <v>Inventory</v>
@@ -8800,11 +8806,8 @@
         <f t="shared" si="28"/>
         <v>-277.12085092026518</v>
       </c>
-      <c r="U68" s="28" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.45">
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B69" s="34" t="str">
         <f>'Manual Data'!B6</f>
         <v>Payables</v>
@@ -8870,7 +8873,7 @@
         <v>609.85989309060642</v>
       </c>
     </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B70" s="34" t="str">
         <f>'Manual Data'!B7</f>
         <v>Loans Advances</v>
@@ -8936,7 +8939,7 @@
         <v>-187.18002176320533</v>
       </c>
     </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B71" s="34" t="str">
         <f>'Manual Data'!B8</f>
         <v>Other WC items</v>
@@ -9002,7 +9005,7 @@
         <v>1619.3683585573654</v>
       </c>
     </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B72" s="34" t="str">
         <f>'Manual Data'!B9</f>
         <v>Working capital changes</v>
@@ -9068,7 +9071,7 @@
         <v>1475.911439897784</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B73" s="34" t="str">
         <f>'Manual Data'!B10</f>
         <v>Direct taxes</v>
@@ -9134,7 +9137,7 @@
         <v>-4999.0491689071196</v>
       </c>
     </row>
-    <row r="74" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="74" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B74" s="34" t="str">
         <f>'Manual Data'!B11</f>
         <v>Other operating items</v>
@@ -9200,7 +9203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:21" s="31" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:17" s="31" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B75" s="25" t="str">
         <f>'Manual Data'!B12</f>
         <v>Cash-Flow from Operating Activity</v>
@@ -9266,14 +9269,14 @@
         <v>16601.896143577182</v>
       </c>
     </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:17" x14ac:dyDescent="0.45">
       <c r="M76" s="193"/>
       <c r="N76" s="193"/>
       <c r="O76" s="193"/>
       <c r="P76" s="193"/>
       <c r="Q76" s="193"/>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B77" s="24" t="str">
         <f>'Manual Data'!B14</f>
         <v>Cash from Investing Activity </v>
@@ -9284,7 +9287,7 @@
       <c r="P77" s="193"/>
       <c r="Q77" s="193"/>
     </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B78" s="34" t="str">
         <f>'Manual Data'!B15</f>
         <v>Fixed assets purchased</v>
@@ -9350,7 +9353,7 @@
         <v>-2524.800134259699</v>
       </c>
     </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B79" s="34" t="str">
         <f>'Manual Data'!B16</f>
         <v>Fixed assets sold</v>
@@ -9411,7 +9414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B80" s="34" t="str">
         <f>'Manual Data'!B17</f>
         <v>Investments purchased</v>
@@ -10474,7 +10477,7 @@
     </row>
     <row r="99" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B99" s="24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C99" s="67">
         <f>C101-C100</f>
@@ -10606,7 +10609,7 @@
     </row>
     <row r="101" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B101" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C101" s="67">
         <f>C58</f>
@@ -11528,13 +11531,13 @@
         <f t="shared" si="20"/>
         <v>2.0515151514793648E-2</v>
       </c>
-      <c r="R19" s="236" t="s">
-        <v>229</v>
-      </c>
-      <c r="S19" s="237"/>
-      <c r="T19" s="237"/>
-      <c r="U19" s="237"/>
-      <c r="V19" s="237"/>
+      <c r="R19" s="242" t="s">
+        <v>228</v>
+      </c>
+      <c r="S19" s="243"/>
+      <c r="T19" s="243"/>
+      <c r="U19" s="243"/>
+      <c r="V19" s="243"/>
       <c r="W19" s="168"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.45">
@@ -11846,13 +11849,13 @@
       <c r="N25" s="195"/>
       <c r="O25" s="195"/>
       <c r="P25" s="195"/>
-      <c r="R25" s="236" t="s">
+      <c r="R25" s="242" t="s">
         <v>222</v>
       </c>
-      <c r="S25" s="237"/>
-      <c r="T25" s="237"/>
-      <c r="U25" s="237"/>
-      <c r="V25" s="238"/>
+      <c r="S25" s="243"/>
+      <c r="T25" s="243"/>
+      <c r="U25" s="243"/>
+      <c r="V25" s="244"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="L26" s="195"/>
@@ -12517,13 +12520,13 @@
       <c r="O39" s="208"/>
       <c r="P39" s="208"/>
       <c r="Q39" s="129"/>
-      <c r="R39" s="236" t="s">
+      <c r="R39" s="242" t="s">
         <v>224</v>
       </c>
-      <c r="S39" s="237"/>
-      <c r="T39" s="237"/>
-      <c r="U39" s="237"/>
-      <c r="V39" s="238"/>
+      <c r="S39" s="243"/>
+      <c r="T39" s="243"/>
+      <c r="U39" s="243"/>
+      <c r="V39" s="244"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.45">
       <c r="L40" s="195"/>
@@ -14600,25 +14603,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="233" t="str">
+      <c r="B1" s="239" t="str">
         <f>"Ratio Analysis for "&amp;'Data Sheet'!B1</f>
         <v>Ratio Analysis for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
+      <c r="M1" s="239"/>
+      <c r="N1" s="239"/>
+      <c r="O1" s="239"/>
+      <c r="P1" s="239"/>
+      <c r="Q1" s="239"/>
     </row>
     <row r="2" spans="2:18" s="44" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="43" t="str">
@@ -16712,36 +16715,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="233" t="str">
+      <c r="B1" s="239" t="str">
         <f>"DCF Model for "&amp;'Data Sheet'!B1</f>
         <v>DCF Model for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
     </row>
     <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="242" t="str">
+      <c r="B2" s="238" t="str">
         <f>"WACC Calculation for "&amp;'Data Sheet'!B1</f>
         <v>WACC Calculation for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="242"/>
-      <c r="E2" s="239" t="str">
+      <c r="C2" s="238"/>
+      <c r="E2" s="235" t="str">
         <f>"Discount Cash-Flow for "&amp;'Data Sheet'!B1</f>
         <v>Discount Cash-Flow for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="241"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="237"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B3" s="83" t="s">
@@ -16921,7 +16924,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="225" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F8" s="226">
         <f>SUM('Historical Financial Statement'!L56:L57)-'Historical Financial Statement'!L36</f>
@@ -16956,10 +16959,10 @@
         <v>7.2900000000000006E-2</v>
       </c>
       <c r="E9" s="218" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="63" t="s">
         <v>236</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>237</v>
       </c>
       <c r="G9" s="102">
         <f>IFERROR(G8-F8,G8)</f>
@@ -17037,7 +17040,7 @@
       </c>
       <c r="F12" s="79"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="97">
+      <c r="H12" s="234">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
@@ -17241,33 +17244,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="233" t="str">
+      <c r="B1" s="239" t="str">
         <f>"BETA(L) Calculation for "&amp;'Data Sheet'!B1</f>
         <v>BETA(L) Calculation for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="243" t="str">
+      <c r="B2" s="245" t="str">
         <f>'Data Sheet'!B1</f>
         <v>HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="243"/>
-      <c r="D2" s="243"/>
-      <c r="F2" s="243" t="s">
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="F2" s="245" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="243"/>
-      <c r="H2" s="243"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="245"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="79" t="s">
@@ -17333,10 +17336,10 @@
         <f t="shared" si="1"/>
         <v>-6.9758819206544587E-3</v>
       </c>
-      <c r="K5" s="244" t="s">
+      <c r="K5" s="246" t="s">
         <v>148</v>
       </c>
-      <c r="L5" s="244"/>
+      <c r="L5" s="246"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" s="80">
@@ -29363,49 +29366,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="246" t="str">
+      <c r="B2" s="248" t="str">
         <f>"COMP Analysis for "&amp;'Data Sheet'!B1</f>
         <v>COMP Analysis for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C2" s="246"/>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="246"/>
-      <c r="H2" s="246"/>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="M2" s="246"/>
-      <c r="N2" s="246"/>
-      <c r="O2" s="246"/>
-      <c r="P2" s="246"/>
-      <c r="Q2" s="246"/>
+      <c r="C2" s="248"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="248"/>
+      <c r="N2" s="248"/>
+      <c r="O2" s="248"/>
+      <c r="P2" s="248"/>
+      <c r="Q2" s="248"/>
     </row>
     <row r="3" spans="2:18" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="112"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="247" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
-      <c r="G3" s="245"/>
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="247"/>
       <c r="H3" s="105"/>
-      <c r="I3" s="245" t="s">
+      <c r="I3" s="247" t="s">
         <v>187</v>
       </c>
-      <c r="J3" s="245"/>
-      <c r="K3" s="245"/>
-      <c r="L3" s="245"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
       <c r="M3" s="105"/>
-      <c r="N3" s="245" t="s">
+      <c r="N3" s="247" t="s">
         <v>191</v>
       </c>
-      <c r="O3" s="245"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
+      <c r="O3" s="247"/>
+      <c r="P3" s="247"/>
+      <c r="Q3" s="247"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B4" s="112" t="s">
@@ -29560,7 +29563,7 @@
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B7" s="81" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" s="123">
         <v>1219</v>
@@ -29611,7 +29614,7 @@
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B8" s="81" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C8" s="123">
         <v>409</v>
@@ -29662,7 +29665,7 @@
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B9" s="81" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C9" s="123">
         <v>4677</v>
@@ -29911,12 +29914,12 @@
       </c>
     </row>
     <row r="18" spans="2:17" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="N18" s="245" t="s">
+      <c r="N18" s="247" t="s">
         <v>191</v>
       </c>
-      <c r="O18" s="245"/>
-      <c r="P18" s="245"/>
-      <c r="Q18" s="245"/>
+      <c r="O18" s="247"/>
+      <c r="P18" s="247"/>
+      <c r="Q18" s="247"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B19" s="121" t="str">
@@ -29953,8 +29956,8 @@
         <v>436288.41018646461</v>
       </c>
       <c r="Q20" s="164">
-        <f t="shared" si="12"/>
-        <v>630592.44226418203</v>
+        <f>Q22+Q21</f>
+        <v>629087.44226418203</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.45">
@@ -29995,8 +29998,8 @@
         <v>437793.41018646461</v>
       </c>
       <c r="Q22" s="164">
-        <f t="shared" si="14"/>
-        <v>632097.44226418203</v>
+        <f>Q14*L5</f>
+        <v>630592.44226418203</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.45">
@@ -30049,7 +30052,7 @@
       </c>
       <c r="Q24" s="212">
         <f t="shared" si="16"/>
-        <v>2695.6890532596799</v>
+        <v>2689.2707200188056</v>
       </c>
     </row>
   </sheetData>
@@ -30061,6 +30064,7 @@
     <mergeCell ref="N18:Q18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30074,25 +30078,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" s="46" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="233" t="str">
+      <c r="B1" s="239" t="str">
         <f>"Dupont Model for "&amp;'Data Sheet'!B1</f>
         <v>Dupont Model for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
+      <c r="M1" s="239"/>
+      <c r="N1" s="239"/>
+      <c r="O1" s="239"/>
+      <c r="P1" s="239"/>
+      <c r="Q1" s="239"/>
     </row>
     <row r="2" spans="2:17" s="44" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="43" t="str">
@@ -30551,24 +30555,24 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B12" s="247" t="s">
+      <c r="B12" s="249" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="248"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
-      <c r="M12" s="248"/>
-      <c r="N12" s="248"/>
-      <c r="O12" s="248"/>
-      <c r="P12" s="248"/>
-      <c r="Q12" s="249"/>
+      <c r="C12" s="250"/>
+      <c r="D12" s="250"/>
+      <c r="E12" s="250"/>
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="250"/>
+      <c r="J12" s="250"/>
+      <c r="K12" s="250"/>
+      <c r="L12" s="250"/>
+      <c r="M12" s="250"/>
+      <c r="N12" s="250"/>
+      <c r="O12" s="250"/>
+      <c r="P12" s="250"/>
+      <c r="Q12" s="251"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B13" s="53" t="str">
@@ -30702,24 +30706,24 @@
       </c>
     </row>
     <row r="18" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B18" s="247" t="s">
+      <c r="B18" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="248"/>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
-      <c r="M18" s="248"/>
-      <c r="N18" s="248"/>
-      <c r="O18" s="248"/>
-      <c r="P18" s="248"/>
-      <c r="Q18" s="249"/>
+      <c r="C18" s="250"/>
+      <c r="D18" s="250"/>
+      <c r="E18" s="250"/>
+      <c r="F18" s="250"/>
+      <c r="G18" s="250"/>
+      <c r="H18" s="250"/>
+      <c r="I18" s="250"/>
+      <c r="J18" s="250"/>
+      <c r="K18" s="250"/>
+      <c r="L18" s="250"/>
+      <c r="M18" s="250"/>
+      <c r="N18" s="250"/>
+      <c r="O18" s="250"/>
+      <c r="P18" s="250"/>
+      <c r="Q18" s="251"/>
     </row>
     <row r="19" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="39" t="str">
@@ -30872,20 +30876,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="250" t="str">
+      <c r="B1" s="252" t="str">
         <f>"Common Size Income Statement for "&amp;'Data Sheet'!B1</f>
         <v>Common Size Income Statement for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="251"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="253"/>
     </row>
     <row r="2" spans="2:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="126" t="str">
@@ -31716,20 +31720,20 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="250" t="str">
+      <c r="B22" s="252" t="str">
         <f>"Common Size Balance Sheet for "&amp;'Data Sheet'!B1</f>
         <v>Common Size Balance Sheet for HINDUSTAN UNILEVER LTD</v>
       </c>
-      <c r="C22" s="233"/>
-      <c r="D22" s="233"/>
-      <c r="E22" s="233"/>
-      <c r="F22" s="233"/>
-      <c r="G22" s="233"/>
-      <c r="H22" s="233"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="233"/>
-      <c r="K22" s="233"/>
-      <c r="L22" s="251"/>
+      <c r="C22" s="239"/>
+      <c r="D22" s="239"/>
+      <c r="E22" s="239"/>
+      <c r="F22" s="239"/>
+      <c r="G22" s="239"/>
+      <c r="H22" s="239"/>
+      <c r="I22" s="239"/>
+      <c r="J22" s="239"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="253"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B23" s="126" t="str">
